--- a/dist/templates/SY1 Sem 4.xlsx
+++ b/dist/templates/SY1 Sem 4.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Old Downloads\Downloads\WT DBMS CIE Project\Sample Excel Sheets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Old Downloads\Downloads\Automated Academic Report System\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F921F143-CE21-4E54-8D07-2AA372271BE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CE73EDB-4A40-4C7D-9B9C-74509DAED30D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" xr2:uid="{9825C9CF-F468-4764-ACEF-73A7F80F2223}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="174">
   <si>
     <t>Marathwada Mitra Mandal's</t>
   </si>
@@ -552,244 +552,16 @@
     <t>Email</t>
   </si>
   <si>
-    <t>tusharborate2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>sahilveer2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>vishweshbhilare2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>abhijitbedse2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>pravinambhore2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>avishkarpatil2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>neelkadam2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>kshitijbhate2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>maheshgaikwad2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>poojaumare2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>ayushchandekar2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>ritikmirase2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>vedantikaranaware2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>rugveddeshwant2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>swaradadeshpande2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>jahnavidhanapune2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>vaidehishinde2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>yugantvarekar2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>sajireedamle2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>yashmore2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>gayatridethe2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>srushtishewale2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>shravanipataskar2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>jidnyasapatil2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>ashutoshkulkarni2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>balrajrasal2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>anulaborse2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>gunajimohite2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>altamashmujawar2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>rajkumarmarathe2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>ashleshahumne2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>vikrantdagadkhair2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>jayantraut2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>abhijeethake2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>dnyaneshwarithorat2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>arihantborge2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>pruthvirajkokate2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>rajmohale2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>prathameshkirtane2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>sohambadarkhe2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>shivtejwagare2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>shubhamdorake2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>sanskrutigudhe2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>tanvikavate2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>sohamgawde2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>parthkshirsagar2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>anuragpatil2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>rohanmali2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>ishapatil2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>parthchaudhari2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>khileshchaudhari2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>yagneshpaliwal2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>animishdeo2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>asmitatawar2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>nirajfegade2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>janhavipatil2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>omchandurkar2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>atharvabhonde2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>srujalbhonde2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>parthtopale2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>niranjanmule2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>riteshmanthole2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>krishakulkarni2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>aayushjoshi2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>renukakulkarni2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>divyanshrai2024.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>sumitbhamare2025.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>vedantikamahadik2025.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>shreyashivade2025.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>dnyaneshwarithombal2025.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>diksharupnawar2025.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>shrutidalvi2025.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>tanvidongare2025.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>omkarkulkarni2025.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>prarthanakumbhar2025.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
-    <t>saniyashaikh2025.comp@mmcoe.edu.in</t>
-  </si>
-  <si>
     <t>IV</t>
+  </si>
+  <si>
+    <t>parthlearner@gmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm:ss"/>
-  </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -847,8 +619,9 @@
       <family val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -868,7 +641,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -1094,22 +867,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1140,15 +903,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1254,8 +1008,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1700,30 +1458,30 @@
   <cols>
     <col min="1" max="1" width="5.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="36.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.77734375" customWidth="1"/>
+    <col min="4" max="4" width="14.88671875" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="13.88671875" customWidth="1"/>
+    <col min="7" max="7" width="10.109375" customWidth="1"/>
+    <col min="8" max="8" width="41.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="20.7" x14ac:dyDescent="0.35">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="25"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="22"/>
       <c r="N1" s="5"/>
       <c r="O1" s="5"/>
       <c r="P1" s="5"/>
@@ -1731,21 +1489,21 @@
       <c r="R1" s="5"/>
     </row>
     <row r="2" spans="1:18" ht="22.55" x14ac:dyDescent="0.35">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-      <c r="L2" s="21"/>
-      <c r="M2" s="22"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="19"/>
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
       <c r="P2" s="6"/>
@@ -1753,21 +1511,21 @@
       <c r="R2" s="6"/>
     </row>
     <row r="3" spans="1:18" ht="16.3" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
-      <c r="L3" s="18"/>
-      <c r="M3" s="19"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="15"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="16"/>
       <c r="N3" s="7"/>
       <c r="O3" s="7"/>
       <c r="P3" s="7"/>
@@ -1796,21 +1554,21 @@
     </row>
     <row r="5" spans="1:18" ht="18.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
-      <c r="B5" s="34" t="s">
+      <c r="B5" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="35"/>
-      <c r="D5" s="36"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="33"/>
       <c r="E5" s="8"/>
-      <c r="F5" s="49" t="s">
+      <c r="F5" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="50"/>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="50"/>
-      <c r="K5" s="50"/>
-      <c r="L5" s="51"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
+      <c r="I5" s="47"/>
+      <c r="J5" s="47"/>
+      <c r="K5" s="47"/>
+      <c r="L5" s="48"/>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1820,21 +1578,21 @@
     </row>
     <row r="6" spans="1:18" ht="18.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3"/>
-      <c r="B6" s="37" t="s">
+      <c r="B6" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="38"/>
-      <c r="D6" s="39"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="36"/>
       <c r="E6" s="8"/>
-      <c r="F6" s="43" t="s">
+      <c r="F6" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="44"/>
-      <c r="L6" s="45"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="42"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
       <c r="P6" s="2"/>
@@ -1843,21 +1601,21 @@
     </row>
     <row r="7" spans="1:18" ht="18.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="25" t="s">
         <v>145</v>
       </c>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="26"/>
       <c r="E7" s="8"/>
-      <c r="F7" s="30" t="s">
+      <c r="F7" s="27" t="s">
         <v>146</v>
       </c>
-      <c r="G7" s="30"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="30"/>
-      <c r="J7" s="30"/>
-      <c r="K7" s="30"/>
-      <c r="L7" s="31"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="27"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="27"/>
+      <c r="L7" s="28"/>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
       <c r="P7" s="2"/>
@@ -1866,21 +1624,21 @@
     </row>
     <row r="8" spans="1:18" ht="18.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4"/>
-      <c r="B8" s="40" t="s">
+      <c r="B8" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="41"/>
-      <c r="D8" s="42"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="39"/>
       <c r="E8" s="8"/>
-      <c r="F8" s="46" t="s">
+      <c r="F8" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="G8" s="47"/>
-      <c r="H8" s="47"/>
-      <c r="I8" s="47"/>
-      <c r="J8" s="47"/>
-      <c r="K8" s="47"/>
-      <c r="L8" s="48"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="44"/>
+      <c r="K8" s="44"/>
+      <c r="L8" s="45"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1890,21 +1648,21 @@
     </row>
     <row r="9" spans="1:18" ht="18.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4"/>
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="23" t="s">
         <v>144</v>
       </c>
-      <c r="C9" s="27"/>
-      <c r="D9" s="27"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
       <c r="E9" s="8"/>
-      <c r="F9" s="32" t="s">
-        <v>248</v>
-      </c>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
-      <c r="K9" s="32"/>
-      <c r="L9" s="33"/>
+      <c r="F9" s="29" t="s">
+        <v>172</v>
+      </c>
+      <c r="G9" s="29"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="29"/>
+      <c r="L9" s="30"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1937,6 +1695,13 @@
       <c r="H11" s="9" t="s">
         <v>171</v>
       </c>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="9"/>
+      <c r="O11" s="9"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="11">
@@ -1948,13 +1713,28 @@
       <c r="C12" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="14" t="s">
-        <v>172</v>
-      </c>
+      <c r="D12" s="11">
+        <v>16</v>
+      </c>
+      <c r="E12" s="11">
+        <v>10</v>
+      </c>
+      <c r="F12" s="11">
+        <v>9</v>
+      </c>
+      <c r="G12" s="11">
+        <v>10</v>
+      </c>
+      <c r="H12" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="11"/>
+      <c r="O12" s="11"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="11">
@@ -1966,13 +1746,28 @@
       <c r="C13" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="14" t="s">
-        <v>173</v>
-      </c>
+      <c r="D13" s="11">
+        <v>16</v>
+      </c>
+      <c r="E13" s="11">
+        <v>11</v>
+      </c>
+      <c r="F13" s="11">
+        <v>14</v>
+      </c>
+      <c r="G13" s="11">
+        <v>13</v>
+      </c>
+      <c r="H13" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="11"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="11">
@@ -1984,13 +1779,28 @@
       <c r="C14" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="14" t="s">
-        <v>174</v>
-      </c>
+      <c r="D14" s="11">
+        <v>16</v>
+      </c>
+      <c r="E14" s="11">
+        <v>15</v>
+      </c>
+      <c r="F14" s="11">
+        <v>13</v>
+      </c>
+      <c r="G14" s="11">
+        <v>16</v>
+      </c>
+      <c r="H14" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="11"/>
+      <c r="O14" s="11"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="11">
@@ -2002,13 +1812,28 @@
       <c r="C15" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="14" t="s">
-        <v>175</v>
-      </c>
+      <c r="D15" s="11">
+        <v>7</v>
+      </c>
+      <c r="E15" s="11">
+        <v>5</v>
+      </c>
+      <c r="F15" s="11">
+        <v>6</v>
+      </c>
+      <c r="G15" s="11">
+        <v>9</v>
+      </c>
+      <c r="H15" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="11"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="11">
@@ -2020,15 +1845,30 @@
       <c r="C16" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="14" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D16" s="11">
+        <v>15</v>
+      </c>
+      <c r="E16" s="11">
+        <v>13</v>
+      </c>
+      <c r="F16" s="11">
+        <v>5</v>
+      </c>
+      <c r="G16" s="11">
+        <v>7</v>
+      </c>
+      <c r="H16" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="11"/>
+      <c r="N16" s="11"/>
+      <c r="O16" s="11"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="11">
         <v>6</v>
       </c>
@@ -2038,15 +1878,30 @@
       <c r="C17" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="14" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D17" s="11">
+        <v>15</v>
+      </c>
+      <c r="E17" s="11">
+        <v>9</v>
+      </c>
+      <c r="F17" s="11">
+        <v>6</v>
+      </c>
+      <c r="G17" s="11">
+        <v>6</v>
+      </c>
+      <c r="H17" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="11"/>
+      <c r="O17" s="11"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="11">
         <v>7</v>
       </c>
@@ -2056,15 +1911,30 @@
       <c r="C18" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="14" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D18" s="11">
+        <v>14</v>
+      </c>
+      <c r="E18" s="11">
+        <v>14</v>
+      </c>
+      <c r="F18" s="11">
+        <v>6</v>
+      </c>
+      <c r="G18" s="11">
+        <v>9</v>
+      </c>
+      <c r="H18" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="11"/>
+      <c r="O18" s="11"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="11">
         <v>8</v>
       </c>
@@ -2074,15 +1944,30 @@
       <c r="C19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="14" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D19" s="11">
+        <v>13</v>
+      </c>
+      <c r="E19" s="11">
+        <v>12</v>
+      </c>
+      <c r="F19" s="11">
+        <v>3</v>
+      </c>
+      <c r="G19" s="11">
+        <v>3</v>
+      </c>
+      <c r="H19" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="11"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="11">
         <v>9</v>
       </c>
@@ -2092,15 +1977,30 @@
       <c r="C20" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="14" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D20" s="11">
+        <v>15</v>
+      </c>
+      <c r="E20" s="11">
+        <v>10</v>
+      </c>
+      <c r="F20" s="11">
+        <v>6</v>
+      </c>
+      <c r="G20" s="11">
+        <v>6</v>
+      </c>
+      <c r="H20" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
+      <c r="M20" s="11"/>
+      <c r="N20" s="11"/>
+      <c r="O20" s="11"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="11">
         <v>10</v>
       </c>
@@ -2110,15 +2010,30 @@
       <c r="C21" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="14" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D21" s="11">
+        <v>7</v>
+      </c>
+      <c r="E21" s="11">
+        <v>7</v>
+      </c>
+      <c r="F21" s="11">
+        <v>3</v>
+      </c>
+      <c r="G21" s="11">
+        <v>4</v>
+      </c>
+      <c r="H21" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="11"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="11">
         <v>11</v>
       </c>
@@ -2128,15 +2043,30 @@
       <c r="C22" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="14" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D22" s="11">
+        <v>10</v>
+      </c>
+      <c r="E22" s="11">
+        <v>5</v>
+      </c>
+      <c r="F22" s="11">
+        <v>1</v>
+      </c>
+      <c r="G22" s="11">
+        <v>0</v>
+      </c>
+      <c r="H22" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11"/>
+      <c r="N22" s="11"/>
+      <c r="O22" s="11"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="11">
         <v>12</v>
       </c>
@@ -2146,15 +2076,30 @@
       <c r="C23" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="14" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D23" s="11">
+        <v>11</v>
+      </c>
+      <c r="E23" s="11">
+        <v>8</v>
+      </c>
+      <c r="F23" s="11">
+        <v>8</v>
+      </c>
+      <c r="G23" s="11">
+        <v>2</v>
+      </c>
+      <c r="H23" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="11"/>
+      <c r="O23" s="11"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="11">
         <v>13</v>
       </c>
@@ -2164,15 +2109,30 @@
       <c r="C24" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="14" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D24" s="11">
+        <v>12</v>
+      </c>
+      <c r="E24" s="11">
+        <v>15</v>
+      </c>
+      <c r="F24" s="11">
+        <v>14</v>
+      </c>
+      <c r="G24" s="11">
+        <v>16</v>
+      </c>
+      <c r="H24" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
+      <c r="N24" s="11"/>
+      <c r="O24" s="11"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="11">
         <v>14</v>
       </c>
@@ -2182,15 +2142,30 @@
       <c r="C25" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="14" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D25" s="11">
+        <v>14</v>
+      </c>
+      <c r="E25" s="11">
+        <v>13</v>
+      </c>
+      <c r="F25" s="11">
+        <v>12</v>
+      </c>
+      <c r="G25" s="11">
+        <v>9</v>
+      </c>
+      <c r="H25" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+      <c r="N25" s="11"/>
+      <c r="O25" s="11"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="11">
         <v>15</v>
       </c>
@@ -2200,15 +2175,30 @@
       <c r="C26" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="14" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D26" s="11">
+        <v>10</v>
+      </c>
+      <c r="E26" s="11">
+        <v>13</v>
+      </c>
+      <c r="F26" s="11">
+        <v>6</v>
+      </c>
+      <c r="G26" s="11">
+        <v>13</v>
+      </c>
+      <c r="H26" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I26" s="11"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="11"/>
+      <c r="M26" s="11"/>
+      <c r="N26" s="11"/>
+      <c r="O26" s="11"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="11">
         <v>16</v>
       </c>
@@ -2218,15 +2208,30 @@
       <c r="C27" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="14" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D27" s="11">
+        <v>14</v>
+      </c>
+      <c r="E27" s="11">
+        <v>12</v>
+      </c>
+      <c r="F27" s="11">
+        <v>6</v>
+      </c>
+      <c r="G27" s="11">
+        <v>9</v>
+      </c>
+      <c r="H27" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+      <c r="N27" s="11"/>
+      <c r="O27" s="11"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="11">
         <v>17</v>
       </c>
@@ -2236,15 +2241,30 @@
       <c r="C28" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="14" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D28" s="11">
+        <v>13</v>
+      </c>
+      <c r="E28" s="11">
+        <v>15</v>
+      </c>
+      <c r="F28" s="11">
+        <v>14</v>
+      </c>
+      <c r="G28" s="11">
+        <v>16</v>
+      </c>
+      <c r="H28" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I28" s="11"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="11"/>
+      <c r="M28" s="11"/>
+      <c r="N28" s="11"/>
+      <c r="O28" s="11"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="11">
         <v>18</v>
       </c>
@@ -2254,15 +2274,30 @@
       <c r="C29" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="14" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D29" s="11">
+        <v>13</v>
+      </c>
+      <c r="E29" s="11">
+        <v>13</v>
+      </c>
+      <c r="F29" s="11">
+        <v>15</v>
+      </c>
+      <c r="G29" s="11">
+        <v>12</v>
+      </c>
+      <c r="H29" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+      <c r="M29" s="11"/>
+      <c r="N29" s="11"/>
+      <c r="O29" s="11"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="11">
         <v>19</v>
       </c>
@@ -2272,15 +2307,30 @@
       <c r="C30" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="14" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D30" s="11">
+        <v>14</v>
+      </c>
+      <c r="E30" s="11">
+        <v>16</v>
+      </c>
+      <c r="F30" s="11">
+        <v>14</v>
+      </c>
+      <c r="G30" s="11">
+        <v>12</v>
+      </c>
+      <c r="H30" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="11"/>
+      <c r="N30" s="11"/>
+      <c r="O30" s="11"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="11">
         <v>20</v>
       </c>
@@ -2290,15 +2340,30 @@
       <c r="C31" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="14" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D31" s="11">
+        <v>5</v>
+      </c>
+      <c r="E31" s="11">
+        <v>6</v>
+      </c>
+      <c r="F31" s="11">
+        <v>6</v>
+      </c>
+      <c r="G31" s="11">
+        <v>7</v>
+      </c>
+      <c r="H31" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I31" s="11"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+      <c r="M31" s="11"/>
+      <c r="N31" s="11"/>
+      <c r="O31" s="11"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="11">
         <v>21</v>
       </c>
@@ -2308,15 +2373,30 @@
       <c r="C32" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="14" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D32" s="11">
+        <v>11</v>
+      </c>
+      <c r="E32" s="11">
+        <v>9</v>
+      </c>
+      <c r="F32" s="11">
+        <v>7</v>
+      </c>
+      <c r="G32" s="11">
+        <v>8</v>
+      </c>
+      <c r="H32" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="11"/>
+      <c r="N32" s="11"/>
+      <c r="O32" s="11"/>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" s="11">
         <v>22</v>
       </c>
@@ -2326,15 +2406,30 @@
       <c r="C33" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="14" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D33" s="11">
+        <v>8</v>
+      </c>
+      <c r="E33" s="11">
+        <v>7</v>
+      </c>
+      <c r="F33" s="11">
+        <v>6</v>
+      </c>
+      <c r="G33" s="11">
+        <v>11</v>
+      </c>
+      <c r="H33" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
+      <c r="M33" s="11"/>
+      <c r="N33" s="11"/>
+      <c r="O33" s="11"/>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" s="11">
         <v>23</v>
       </c>
@@ -2344,15 +2439,30 @@
       <c r="C34" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="14" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D34" s="11">
+        <v>16</v>
+      </c>
+      <c r="E34" s="11">
+        <v>16</v>
+      </c>
+      <c r="F34" s="11">
+        <v>14</v>
+      </c>
+      <c r="G34" s="11">
+        <v>14</v>
+      </c>
+      <c r="H34" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I34" s="11"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="11"/>
+      <c r="N34" s="11"/>
+      <c r="O34" s="11"/>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" s="11">
         <v>24</v>
       </c>
@@ -2362,15 +2472,30 @@
       <c r="C35" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="14" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D35" s="11">
+        <v>16</v>
+      </c>
+      <c r="E35" s="11">
+        <v>16</v>
+      </c>
+      <c r="F35" s="11">
+        <v>15</v>
+      </c>
+      <c r="G35" s="11">
+        <v>13</v>
+      </c>
+      <c r="H35" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I35" s="11"/>
+      <c r="J35" s="11"/>
+      <c r="K35" s="11"/>
+      <c r="L35" s="11"/>
+      <c r="M35" s="11"/>
+      <c r="N35" s="11"/>
+      <c r="O35" s="11"/>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" s="11">
         <v>25</v>
       </c>
@@ -2380,15 +2505,30 @@
       <c r="C36" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="11"/>
-      <c r="H36" s="14" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D36" s="11">
+        <v>13</v>
+      </c>
+      <c r="E36" s="11">
+        <v>14</v>
+      </c>
+      <c r="F36" s="11">
+        <v>7</v>
+      </c>
+      <c r="G36" s="11">
+        <v>12</v>
+      </c>
+      <c r="H36" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I36" s="11"/>
+      <c r="J36" s="11"/>
+      <c r="K36" s="11"/>
+      <c r="L36" s="11"/>
+      <c r="M36" s="11"/>
+      <c r="N36" s="11"/>
+      <c r="O36" s="11"/>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" s="11">
         <v>26</v>
       </c>
@@ -2398,15 +2538,30 @@
       <c r="C37" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="14" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D37" s="11">
+        <v>9</v>
+      </c>
+      <c r="E37" s="11">
+        <v>4</v>
+      </c>
+      <c r="F37" s="11">
+        <v>6</v>
+      </c>
+      <c r="G37" s="11">
+        <v>11</v>
+      </c>
+      <c r="H37" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I37" s="11"/>
+      <c r="J37" s="11"/>
+      <c r="K37" s="11"/>
+      <c r="L37" s="11"/>
+      <c r="M37" s="11"/>
+      <c r="N37" s="11"/>
+      <c r="O37" s="11"/>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" s="11">
         <v>27</v>
       </c>
@@ -2416,15 +2571,30 @@
       <c r="C38" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="D38" s="11"/>
-      <c r="E38" s="11"/>
-      <c r="F38" s="11"/>
-      <c r="G38" s="11"/>
-      <c r="H38" s="14" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D38" s="11">
+        <v>15</v>
+      </c>
+      <c r="E38" s="11">
+        <v>11</v>
+      </c>
+      <c r="F38" s="11">
+        <v>5</v>
+      </c>
+      <c r="G38" s="11">
+        <v>7</v>
+      </c>
+      <c r="H38" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I38" s="11"/>
+      <c r="J38" s="11"/>
+      <c r="K38" s="11"/>
+      <c r="L38" s="11"/>
+      <c r="M38" s="11"/>
+      <c r="N38" s="11"/>
+      <c r="O38" s="11"/>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" s="11">
         <v>28</v>
       </c>
@@ -2434,15 +2604,30 @@
       <c r="C39" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="D39" s="11"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11"/>
-      <c r="G39" s="11"/>
-      <c r="H39" s="14" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D39" s="11">
+        <v>15</v>
+      </c>
+      <c r="E39" s="11">
+        <v>15</v>
+      </c>
+      <c r="F39" s="11">
+        <v>9</v>
+      </c>
+      <c r="G39" s="11">
+        <v>7</v>
+      </c>
+      <c r="H39" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I39" s="11"/>
+      <c r="J39" s="11"/>
+      <c r="K39" s="11"/>
+      <c r="L39" s="11"/>
+      <c r="M39" s="11"/>
+      <c r="N39" s="11"/>
+      <c r="O39" s="11"/>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" s="11">
         <v>29</v>
       </c>
@@ -2452,15 +2637,30 @@
       <c r="C40" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="11"/>
-      <c r="H40" s="14" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D40" s="11">
+        <v>16</v>
+      </c>
+      <c r="E40" s="11">
+        <v>10</v>
+      </c>
+      <c r="F40" s="11">
+        <v>11</v>
+      </c>
+      <c r="G40" s="11">
+        <v>14</v>
+      </c>
+      <c r="H40" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I40" s="11"/>
+      <c r="J40" s="11"/>
+      <c r="K40" s="11"/>
+      <c r="L40" s="11"/>
+      <c r="M40" s="11"/>
+      <c r="N40" s="11"/>
+      <c r="O40" s="11"/>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" s="11">
         <v>30</v>
       </c>
@@ -2470,15 +2670,30 @@
       <c r="C41" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="D41" s="11"/>
-      <c r="E41" s="11"/>
-      <c r="F41" s="11"/>
-      <c r="G41" s="11"/>
-      <c r="H41" s="14" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D41" s="11">
+        <v>14</v>
+      </c>
+      <c r="E41" s="11">
+        <v>14</v>
+      </c>
+      <c r="F41" s="11">
+        <v>10</v>
+      </c>
+      <c r="G41" s="11">
+        <v>11</v>
+      </c>
+      <c r="H41" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I41" s="11"/>
+      <c r="J41" s="11"/>
+      <c r="K41" s="11"/>
+      <c r="L41" s="11"/>
+      <c r="M41" s="11"/>
+      <c r="N41" s="11"/>
+      <c r="O41" s="11"/>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" s="11">
         <v>31</v>
       </c>
@@ -2488,15 +2703,30 @@
       <c r="C42" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="D42" s="11"/>
-      <c r="E42" s="11"/>
-      <c r="F42" s="11"/>
-      <c r="G42" s="11"/>
-      <c r="H42" s="14" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D42" s="11">
+        <v>15</v>
+      </c>
+      <c r="E42" s="11">
+        <v>14</v>
+      </c>
+      <c r="F42" s="11">
+        <v>7</v>
+      </c>
+      <c r="G42" s="11">
+        <v>8</v>
+      </c>
+      <c r="H42" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I42" s="11"/>
+      <c r="J42" s="11"/>
+      <c r="K42" s="11"/>
+      <c r="L42" s="11"/>
+      <c r="M42" s="11"/>
+      <c r="N42" s="11"/>
+      <c r="O42" s="11"/>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" s="11">
         <v>32</v>
       </c>
@@ -2506,15 +2736,30 @@
       <c r="C43" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="D43" s="11"/>
-      <c r="E43" s="11"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="14" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D43" s="11">
+        <v>8</v>
+      </c>
+      <c r="E43" s="11">
+        <v>9</v>
+      </c>
+      <c r="F43" s="11">
+        <v>6</v>
+      </c>
+      <c r="G43" s="11">
+        <v>2</v>
+      </c>
+      <c r="H43" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I43" s="11"/>
+      <c r="J43" s="11"/>
+      <c r="K43" s="11"/>
+      <c r="L43" s="11"/>
+      <c r="M43" s="11"/>
+      <c r="N43" s="11"/>
+      <c r="O43" s="11"/>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" s="11">
         <v>33</v>
       </c>
@@ -2524,15 +2769,30 @@
       <c r="C44" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="D44" s="11"/>
-      <c r="E44" s="11"/>
-      <c r="F44" s="11"/>
-      <c r="G44" s="11"/>
-      <c r="H44" s="14" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D44" s="11">
+        <v>11</v>
+      </c>
+      <c r="E44" s="11">
+        <v>11</v>
+      </c>
+      <c r="F44" s="11">
+        <v>10</v>
+      </c>
+      <c r="G44" s="11">
+        <v>8</v>
+      </c>
+      <c r="H44" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I44" s="11"/>
+      <c r="J44" s="11"/>
+      <c r="K44" s="11"/>
+      <c r="L44" s="11"/>
+      <c r="M44" s="11"/>
+      <c r="N44" s="11"/>
+      <c r="O44" s="11"/>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" s="11">
         <v>34</v>
       </c>
@@ -2542,15 +2802,30 @@
       <c r="C45" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="D45" s="11"/>
-      <c r="E45" s="11"/>
-      <c r="F45" s="11"/>
-      <c r="G45" s="11"/>
-      <c r="H45" s="14" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D45" s="11">
+        <v>16</v>
+      </c>
+      <c r="E45" s="11">
+        <v>11</v>
+      </c>
+      <c r="F45" s="11">
+        <v>10</v>
+      </c>
+      <c r="G45" s="11">
+        <v>13</v>
+      </c>
+      <c r="H45" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I45" s="11"/>
+      <c r="J45" s="11"/>
+      <c r="K45" s="11"/>
+      <c r="L45" s="11"/>
+      <c r="M45" s="11"/>
+      <c r="N45" s="11"/>
+      <c r="O45" s="11"/>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" s="11">
         <v>35</v>
       </c>
@@ -2560,15 +2835,30 @@
       <c r="C46" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="D46" s="11"/>
-      <c r="E46" s="11"/>
-      <c r="F46" s="11"/>
-      <c r="G46" s="11"/>
-      <c r="H46" s="14" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D46" s="11">
+        <v>14</v>
+      </c>
+      <c r="E46" s="11">
+        <v>13</v>
+      </c>
+      <c r="F46" s="11">
+        <v>8</v>
+      </c>
+      <c r="G46" s="11">
+        <v>10</v>
+      </c>
+      <c r="H46" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I46" s="11"/>
+      <c r="J46" s="11"/>
+      <c r="K46" s="11"/>
+      <c r="L46" s="11"/>
+      <c r="M46" s="11"/>
+      <c r="N46" s="11"/>
+      <c r="O46" s="11"/>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" s="11">
         <v>36</v>
       </c>
@@ -2578,15 +2868,30 @@
       <c r="C47" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="D47" s="11"/>
-      <c r="E47" s="11"/>
-      <c r="F47" s="11"/>
-      <c r="G47" s="11"/>
-      <c r="H47" s="14" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D47" s="11">
+        <v>8</v>
+      </c>
+      <c r="E47" s="11">
+        <v>14</v>
+      </c>
+      <c r="F47" s="11">
+        <v>8</v>
+      </c>
+      <c r="G47" s="11">
+        <v>6</v>
+      </c>
+      <c r="H47" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I47" s="11"/>
+      <c r="J47" s="11"/>
+      <c r="K47" s="11"/>
+      <c r="L47" s="11"/>
+      <c r="M47" s="11"/>
+      <c r="N47" s="11"/>
+      <c r="O47" s="11"/>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" s="11">
         <v>37</v>
       </c>
@@ -2596,15 +2901,30 @@
       <c r="C48" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="D48" s="11"/>
-      <c r="E48" s="11"/>
-      <c r="F48" s="11"/>
-      <c r="G48" s="11"/>
-      <c r="H48" s="14" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D48" s="11">
+        <v>12</v>
+      </c>
+      <c r="E48" s="11">
+        <v>14</v>
+      </c>
+      <c r="F48" s="11">
+        <v>5</v>
+      </c>
+      <c r="G48" s="11">
+        <v>7</v>
+      </c>
+      <c r="H48" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I48" s="11"/>
+      <c r="J48" s="11"/>
+      <c r="K48" s="11"/>
+      <c r="L48" s="11"/>
+      <c r="M48" s="11"/>
+      <c r="N48" s="11"/>
+      <c r="O48" s="11"/>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" s="11">
         <v>38</v>
       </c>
@@ -2614,15 +2934,30 @@
       <c r="C49" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="D49" s="11"/>
-      <c r="E49" s="11"/>
-      <c r="F49" s="11"/>
-      <c r="G49" s="11"/>
-      <c r="H49" s="14" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D49" s="11">
+        <v>13</v>
+      </c>
+      <c r="E49" s="11">
+        <v>16</v>
+      </c>
+      <c r="F49" s="11">
+        <v>10</v>
+      </c>
+      <c r="G49" s="11">
+        <v>13</v>
+      </c>
+      <c r="H49" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I49" s="11"/>
+      <c r="J49" s="11"/>
+      <c r="K49" s="11"/>
+      <c r="L49" s="11"/>
+      <c r="M49" s="11"/>
+      <c r="N49" s="11"/>
+      <c r="O49" s="11"/>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" s="11">
         <v>39</v>
       </c>
@@ -2632,15 +2967,30 @@
       <c r="C50" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="D50" s="11"/>
-      <c r="E50" s="11"/>
-      <c r="F50" s="11"/>
-      <c r="G50" s="11"/>
-      <c r="H50" s="14" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D50" s="11">
+        <v>0</v>
+      </c>
+      <c r="E50" s="11">
+        <v>8</v>
+      </c>
+      <c r="F50" s="11">
+        <v>0</v>
+      </c>
+      <c r="G50" s="11">
+        <v>0</v>
+      </c>
+      <c r="H50" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I50" s="11"/>
+      <c r="J50" s="11"/>
+      <c r="K50" s="11"/>
+      <c r="L50" s="11"/>
+      <c r="M50" s="11"/>
+      <c r="N50" s="11"/>
+      <c r="O50" s="11"/>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" s="11">
         <v>40</v>
       </c>
@@ -2650,15 +3000,30 @@
       <c r="C51" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="D51" s="11"/>
-      <c r="E51" s="11"/>
-      <c r="F51" s="11"/>
-      <c r="G51" s="11"/>
-      <c r="H51" s="14" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D51" s="11">
+        <v>11</v>
+      </c>
+      <c r="E51" s="11">
+        <v>12</v>
+      </c>
+      <c r="F51" s="11">
+        <v>8</v>
+      </c>
+      <c r="G51" s="11">
+        <v>7</v>
+      </c>
+      <c r="H51" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I51" s="11"/>
+      <c r="J51" s="11"/>
+      <c r="K51" s="11"/>
+      <c r="L51" s="11"/>
+      <c r="M51" s="11"/>
+      <c r="N51" s="11"/>
+      <c r="O51" s="11"/>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" s="11">
         <v>41</v>
       </c>
@@ -2668,15 +3033,30 @@
       <c r="C52" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="D52" s="11"/>
-      <c r="E52" s="11"/>
-      <c r="F52" s="11"/>
-      <c r="G52" s="11"/>
-      <c r="H52" s="14" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D52" s="11">
+        <v>8</v>
+      </c>
+      <c r="E52" s="11">
+        <v>6</v>
+      </c>
+      <c r="F52" s="11">
+        <v>4</v>
+      </c>
+      <c r="G52" s="11">
+        <v>13</v>
+      </c>
+      <c r="H52" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I52" s="11"/>
+      <c r="J52" s="11"/>
+      <c r="K52" s="11"/>
+      <c r="L52" s="11"/>
+      <c r="M52" s="11"/>
+      <c r="N52" s="11"/>
+      <c r="O52" s="11"/>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" s="11">
         <v>42</v>
       </c>
@@ -2686,15 +3066,30 @@
       <c r="C53" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="D53" s="11"/>
-      <c r="E53" s="11"/>
-      <c r="F53" s="11"/>
-      <c r="G53" s="11"/>
-      <c r="H53" s="14" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D53" s="11">
+        <v>10</v>
+      </c>
+      <c r="E53" s="11">
+        <v>15</v>
+      </c>
+      <c r="F53" s="11">
+        <v>6</v>
+      </c>
+      <c r="G53" s="11">
+        <v>9</v>
+      </c>
+      <c r="H53" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I53" s="11"/>
+      <c r="J53" s="11"/>
+      <c r="K53" s="11"/>
+      <c r="L53" s="11"/>
+      <c r="M53" s="11"/>
+      <c r="N53" s="11"/>
+      <c r="O53" s="11"/>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" s="11">
         <v>43</v>
       </c>
@@ -2704,15 +3099,30 @@
       <c r="C54" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="D54" s="11"/>
-      <c r="E54" s="11"/>
-      <c r="F54" s="11"/>
-      <c r="G54" s="11"/>
-      <c r="H54" s="14" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D54" s="11">
+        <v>10</v>
+      </c>
+      <c r="E54" s="11">
+        <v>12</v>
+      </c>
+      <c r="F54" s="11">
+        <v>10</v>
+      </c>
+      <c r="G54" s="11">
+        <v>13</v>
+      </c>
+      <c r="H54" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I54" s="11"/>
+      <c r="J54" s="11"/>
+      <c r="K54" s="11"/>
+      <c r="L54" s="11"/>
+      <c r="M54" s="11"/>
+      <c r="N54" s="11"/>
+      <c r="O54" s="11"/>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" s="11">
         <v>44</v>
       </c>
@@ -2722,15 +3132,30 @@
       <c r="C55" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="D55" s="11"/>
-      <c r="E55" s="11"/>
-      <c r="F55" s="11"/>
-      <c r="G55" s="11"/>
-      <c r="H55" s="14" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D55" s="11">
+        <v>0</v>
+      </c>
+      <c r="E55" s="11">
+        <v>0</v>
+      </c>
+      <c r="F55" s="11">
+        <v>0</v>
+      </c>
+      <c r="G55" s="11">
+        <v>1</v>
+      </c>
+      <c r="H55" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I55" s="11"/>
+      <c r="J55" s="11"/>
+      <c r="K55" s="11"/>
+      <c r="L55" s="11"/>
+      <c r="M55" s="11"/>
+      <c r="N55" s="11"/>
+      <c r="O55" s="11"/>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" s="11">
         <v>45</v>
       </c>
@@ -2740,15 +3165,30 @@
       <c r="C56" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="D56" s="11"/>
-      <c r="E56" s="11"/>
-      <c r="F56" s="11"/>
-      <c r="G56" s="11"/>
-      <c r="H56" s="14" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D56" s="11">
+        <v>13</v>
+      </c>
+      <c r="E56" s="11">
+        <v>8</v>
+      </c>
+      <c r="F56" s="11">
+        <v>5</v>
+      </c>
+      <c r="G56" s="11">
+        <v>14</v>
+      </c>
+      <c r="H56" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I56" s="11"/>
+      <c r="J56" s="11"/>
+      <c r="K56" s="11"/>
+      <c r="L56" s="11"/>
+      <c r="M56" s="11"/>
+      <c r="N56" s="11"/>
+      <c r="O56" s="11"/>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" s="11">
         <v>46</v>
       </c>
@@ -2758,15 +3198,30 @@
       <c r="C57" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="D57" s="11"/>
-      <c r="E57" s="11"/>
-      <c r="F57" s="11"/>
-      <c r="G57" s="11"/>
-      <c r="H57" s="14" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D57" s="11">
+        <v>13</v>
+      </c>
+      <c r="E57" s="11">
+        <v>14</v>
+      </c>
+      <c r="F57" s="11">
+        <v>7</v>
+      </c>
+      <c r="G57" s="11">
+        <v>6</v>
+      </c>
+      <c r="H57" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I57" s="11"/>
+      <c r="J57" s="11"/>
+      <c r="K57" s="11"/>
+      <c r="L57" s="11"/>
+      <c r="M57" s="11"/>
+      <c r="N57" s="11"/>
+      <c r="O57" s="11"/>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" s="11">
         <v>47</v>
       </c>
@@ -2776,15 +3231,30 @@
       <c r="C58" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="D58" s="11"/>
-      <c r="E58" s="11"/>
-      <c r="F58" s="11"/>
-      <c r="G58" s="11"/>
-      <c r="H58" s="14" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D58" s="11">
+        <v>16</v>
+      </c>
+      <c r="E58" s="11">
+        <v>12</v>
+      </c>
+      <c r="F58" s="11">
+        <v>6</v>
+      </c>
+      <c r="G58" s="11">
+        <v>9</v>
+      </c>
+      <c r="H58" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I58" s="11"/>
+      <c r="J58" s="11"/>
+      <c r="K58" s="11"/>
+      <c r="L58" s="11"/>
+      <c r="M58" s="11"/>
+      <c r="N58" s="11"/>
+      <c r="O58" s="11"/>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" s="11">
         <v>48</v>
       </c>
@@ -2794,15 +3264,30 @@
       <c r="C59" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="D59" s="11"/>
-      <c r="E59" s="11"/>
-      <c r="F59" s="11"/>
-      <c r="G59" s="11"/>
-      <c r="H59" s="14" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D59" s="11">
+        <v>10</v>
+      </c>
+      <c r="E59" s="11">
+        <v>4</v>
+      </c>
+      <c r="F59" s="11">
+        <v>1</v>
+      </c>
+      <c r="G59" s="11">
+        <v>12</v>
+      </c>
+      <c r="H59" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I59" s="11"/>
+      <c r="J59" s="11"/>
+      <c r="K59" s="11"/>
+      <c r="L59" s="11"/>
+      <c r="M59" s="11"/>
+      <c r="N59" s="11"/>
+      <c r="O59" s="11"/>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" s="11">
         <v>49</v>
       </c>
@@ -2812,15 +3297,30 @@
       <c r="C60" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="D60" s="11"/>
-      <c r="E60" s="11"/>
-      <c r="F60" s="11"/>
-      <c r="G60" s="11"/>
-      <c r="H60" s="14" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D60" s="11">
+        <v>12</v>
+      </c>
+      <c r="E60" s="11">
+        <v>14</v>
+      </c>
+      <c r="F60" s="11">
+        <v>14</v>
+      </c>
+      <c r="G60" s="11">
+        <v>9</v>
+      </c>
+      <c r="H60" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I60" s="11"/>
+      <c r="J60" s="11"/>
+      <c r="K60" s="11"/>
+      <c r="L60" s="11"/>
+      <c r="M60" s="11"/>
+      <c r="N60" s="11"/>
+      <c r="O60" s="11"/>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" s="11">
         <v>50</v>
       </c>
@@ -2830,15 +3330,30 @@
       <c r="C61" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="D61" s="11"/>
-      <c r="E61" s="11"/>
-      <c r="F61" s="11"/>
-      <c r="G61" s="11"/>
-      <c r="H61" s="14" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D61" s="11">
+        <v>16</v>
+      </c>
+      <c r="E61" s="11">
+        <v>13</v>
+      </c>
+      <c r="F61" s="11">
+        <v>11</v>
+      </c>
+      <c r="G61" s="11">
+        <v>16</v>
+      </c>
+      <c r="H61" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I61" s="11"/>
+      <c r="J61" s="11"/>
+      <c r="K61" s="11"/>
+      <c r="L61" s="11"/>
+      <c r="M61" s="11"/>
+      <c r="N61" s="11"/>
+      <c r="O61" s="11"/>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" s="11">
         <v>51</v>
       </c>
@@ -2848,15 +3363,30 @@
       <c r="C62" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="D62" s="11"/>
-      <c r="E62" s="11"/>
-      <c r="F62" s="11"/>
-      <c r="G62" s="11"/>
-      <c r="H62" s="14" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D62" s="11">
+        <v>14</v>
+      </c>
+      <c r="E62" s="11">
+        <v>12</v>
+      </c>
+      <c r="F62" s="11">
+        <v>14</v>
+      </c>
+      <c r="G62" s="11">
+        <v>14</v>
+      </c>
+      <c r="H62" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I62" s="11"/>
+      <c r="J62" s="11"/>
+      <c r="K62" s="11"/>
+      <c r="L62" s="11"/>
+      <c r="M62" s="11"/>
+      <c r="N62" s="11"/>
+      <c r="O62" s="11"/>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" s="11">
         <v>52</v>
       </c>
@@ -2866,15 +3396,30 @@
       <c r="C63" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="D63" s="11"/>
-      <c r="E63" s="11"/>
-      <c r="F63" s="11"/>
-      <c r="G63" s="11"/>
-      <c r="H63" s="14" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D63" s="11">
+        <v>15</v>
+      </c>
+      <c r="E63" s="11">
+        <v>9</v>
+      </c>
+      <c r="F63" s="11">
+        <v>16</v>
+      </c>
+      <c r="G63" s="11">
+        <v>11</v>
+      </c>
+      <c r="H63" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I63" s="11"/>
+      <c r="J63" s="11"/>
+      <c r="K63" s="11"/>
+      <c r="L63" s="11"/>
+      <c r="M63" s="11"/>
+      <c r="N63" s="11"/>
+      <c r="O63" s="11"/>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" s="11">
         <v>53</v>
       </c>
@@ -2884,15 +3429,30 @@
       <c r="C64" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="D64" s="11"/>
-      <c r="E64" s="11"/>
-      <c r="F64" s="11"/>
-      <c r="G64" s="11"/>
-      <c r="H64" s="14" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D64" s="11">
+        <v>14</v>
+      </c>
+      <c r="E64" s="11">
+        <v>16</v>
+      </c>
+      <c r="F64" s="11">
+        <v>4</v>
+      </c>
+      <c r="G64" s="11">
+        <v>11</v>
+      </c>
+      <c r="H64" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I64" s="11"/>
+      <c r="J64" s="11"/>
+      <c r="K64" s="11"/>
+      <c r="L64" s="11"/>
+      <c r="M64" s="11"/>
+      <c r="N64" s="11"/>
+      <c r="O64" s="11"/>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" s="11">
         <v>54</v>
       </c>
@@ -2902,15 +3462,30 @@
       <c r="C65" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="D65" s="11"/>
-      <c r="E65" s="11"/>
-      <c r="F65" s="11"/>
-      <c r="G65" s="11"/>
-      <c r="H65" s="14" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D65" s="11">
+        <v>15</v>
+      </c>
+      <c r="E65" s="11">
+        <v>13</v>
+      </c>
+      <c r="F65" s="11">
+        <v>14</v>
+      </c>
+      <c r="G65" s="11">
+        <v>9</v>
+      </c>
+      <c r="H65" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I65" s="11"/>
+      <c r="J65" s="11"/>
+      <c r="K65" s="11"/>
+      <c r="L65" s="11"/>
+      <c r="M65" s="11"/>
+      <c r="N65" s="11"/>
+      <c r="O65" s="11"/>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" s="11">
         <v>55</v>
       </c>
@@ -2920,15 +3495,30 @@
       <c r="C66" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D66" s="11"/>
-      <c r="E66" s="11"/>
-      <c r="F66" s="11"/>
-      <c r="G66" s="11"/>
-      <c r="H66" s="14" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D66" s="11">
+        <v>11</v>
+      </c>
+      <c r="E66" s="11">
+        <v>10</v>
+      </c>
+      <c r="F66" s="11">
+        <v>7</v>
+      </c>
+      <c r="G66" s="11">
+        <v>15</v>
+      </c>
+      <c r="H66" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I66" s="11"/>
+      <c r="J66" s="11"/>
+      <c r="K66" s="11"/>
+      <c r="L66" s="11"/>
+      <c r="M66" s="11"/>
+      <c r="N66" s="11"/>
+      <c r="O66" s="11"/>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67" s="11">
         <v>56</v>
       </c>
@@ -2938,15 +3528,30 @@
       <c r="C67" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="D67" s="11"/>
-      <c r="E67" s="11"/>
-      <c r="F67" s="11"/>
-      <c r="G67" s="11"/>
-      <c r="H67" s="14" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D67" s="11">
+        <v>12</v>
+      </c>
+      <c r="E67" s="11">
+        <v>14</v>
+      </c>
+      <c r="F67" s="11">
+        <v>12</v>
+      </c>
+      <c r="G67" s="11">
+        <v>14</v>
+      </c>
+      <c r="H67" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I67" s="11"/>
+      <c r="J67" s="11"/>
+      <c r="K67" s="11"/>
+      <c r="L67" s="11"/>
+      <c r="M67" s="11"/>
+      <c r="N67" s="11"/>
+      <c r="O67" s="11"/>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68" s="11">
         <v>57</v>
       </c>
@@ -2956,15 +3561,30 @@
       <c r="C68" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="D68" s="11"/>
-      <c r="E68" s="11"/>
-      <c r="F68" s="11"/>
-      <c r="G68" s="11"/>
-      <c r="H68" s="14" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D68" s="11">
+        <v>8</v>
+      </c>
+      <c r="E68" s="11">
+        <v>13</v>
+      </c>
+      <c r="F68" s="11">
+        <v>5</v>
+      </c>
+      <c r="G68" s="11">
+        <v>13</v>
+      </c>
+      <c r="H68" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I68" s="11"/>
+      <c r="J68" s="11"/>
+      <c r="K68" s="11"/>
+      <c r="L68" s="11"/>
+      <c r="M68" s="11"/>
+      <c r="N68" s="11"/>
+      <c r="O68" s="11"/>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69" s="11">
         <v>58</v>
       </c>
@@ -2974,15 +3594,30 @@
       <c r="C69" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D69" s="11"/>
-      <c r="E69" s="11"/>
-      <c r="F69" s="11"/>
-      <c r="G69" s="11"/>
-      <c r="H69" s="14" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D69" s="11">
+        <v>9</v>
+      </c>
+      <c r="E69" s="11">
+        <v>12</v>
+      </c>
+      <c r="F69" s="11">
+        <v>3</v>
+      </c>
+      <c r="G69" s="11">
+        <v>5</v>
+      </c>
+      <c r="H69" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I69" s="11"/>
+      <c r="J69" s="11"/>
+      <c r="K69" s="11"/>
+      <c r="L69" s="11"/>
+      <c r="M69" s="11"/>
+      <c r="N69" s="11"/>
+      <c r="O69" s="11"/>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70" s="11">
         <v>59</v>
       </c>
@@ -2992,15 +3627,30 @@
       <c r="C70" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="D70" s="11"/>
-      <c r="E70" s="11"/>
-      <c r="F70" s="11"/>
-      <c r="G70" s="11"/>
-      <c r="H70" s="14" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D70" s="11">
+        <v>6</v>
+      </c>
+      <c r="E70" s="11">
+        <v>7</v>
+      </c>
+      <c r="F70" s="11">
+        <v>4</v>
+      </c>
+      <c r="G70" s="11">
+        <v>8</v>
+      </c>
+      <c r="H70" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I70" s="11"/>
+      <c r="J70" s="11"/>
+      <c r="K70" s="11"/>
+      <c r="L70" s="11"/>
+      <c r="M70" s="11"/>
+      <c r="N70" s="11"/>
+      <c r="O70" s="11"/>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71" s="11">
         <v>60</v>
       </c>
@@ -3010,15 +3660,30 @@
       <c r="C71" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="D71" s="11"/>
-      <c r="E71" s="11"/>
-      <c r="F71" s="11"/>
-      <c r="G71" s="11"/>
-      <c r="H71" s="14" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D71" s="11">
+        <v>10</v>
+      </c>
+      <c r="E71" s="11">
+        <v>9</v>
+      </c>
+      <c r="F71" s="11">
+        <v>4</v>
+      </c>
+      <c r="G71" s="11">
+        <v>13</v>
+      </c>
+      <c r="H71" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I71" s="11"/>
+      <c r="J71" s="11"/>
+      <c r="K71" s="11"/>
+      <c r="L71" s="11"/>
+      <c r="M71" s="11"/>
+      <c r="N71" s="11"/>
+      <c r="O71" s="11"/>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72" s="11">
         <v>61</v>
       </c>
@@ -3028,15 +3693,30 @@
       <c r="C72" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="D72" s="11"/>
-      <c r="E72" s="11"/>
-      <c r="F72" s="11"/>
-      <c r="G72" s="11"/>
-      <c r="H72" s="14" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D72" s="11">
+        <v>13</v>
+      </c>
+      <c r="E72" s="11">
+        <v>11</v>
+      </c>
+      <c r="F72" s="11">
+        <v>2</v>
+      </c>
+      <c r="G72" s="11">
+        <v>11</v>
+      </c>
+      <c r="H72" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I72" s="11"/>
+      <c r="J72" s="11"/>
+      <c r="K72" s="11"/>
+      <c r="L72" s="11"/>
+      <c r="M72" s="11"/>
+      <c r="N72" s="11"/>
+      <c r="O72" s="11"/>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73" s="11">
         <v>62</v>
       </c>
@@ -3046,15 +3726,30 @@
       <c r="C73" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="D73" s="11"/>
-      <c r="E73" s="11"/>
-      <c r="F73" s="11"/>
-      <c r="G73" s="11"/>
-      <c r="H73" s="14" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D73" s="11">
+        <v>11</v>
+      </c>
+      <c r="E73" s="11">
+        <v>9</v>
+      </c>
+      <c r="F73" s="11">
+        <v>13</v>
+      </c>
+      <c r="G73" s="11">
+        <v>14</v>
+      </c>
+      <c r="H73" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I73" s="11"/>
+      <c r="J73" s="11"/>
+      <c r="K73" s="11"/>
+      <c r="L73" s="11"/>
+      <c r="M73" s="11"/>
+      <c r="N73" s="11"/>
+      <c r="O73" s="11"/>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A74" s="11">
         <v>63</v>
       </c>
@@ -3064,15 +3759,30 @@
       <c r="C74" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="D74" s="11"/>
-      <c r="E74" s="11"/>
-      <c r="F74" s="11"/>
-      <c r="G74" s="11"/>
-      <c r="H74" s="14" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D74" s="11">
+        <v>13</v>
+      </c>
+      <c r="E74" s="11">
+        <v>13</v>
+      </c>
+      <c r="F74" s="11">
+        <v>16</v>
+      </c>
+      <c r="G74" s="11">
+        <v>12</v>
+      </c>
+      <c r="H74" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I74" s="11"/>
+      <c r="J74" s="11"/>
+      <c r="K74" s="11"/>
+      <c r="L74" s="11"/>
+      <c r="M74" s="11"/>
+      <c r="N74" s="11"/>
+      <c r="O74" s="11"/>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75" s="11">
         <v>64</v>
       </c>
@@ -3082,15 +3792,30 @@
       <c r="C75" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="D75" s="11"/>
-      <c r="E75" s="11"/>
-      <c r="F75" s="11"/>
-      <c r="G75" s="11"/>
-      <c r="H75" s="14" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D75" s="11">
+        <v>10</v>
+      </c>
+      <c r="E75" s="11">
+        <v>14</v>
+      </c>
+      <c r="F75" s="11">
+        <v>7</v>
+      </c>
+      <c r="G75" s="11">
+        <v>7</v>
+      </c>
+      <c r="H75" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I75" s="11"/>
+      <c r="J75" s="11"/>
+      <c r="K75" s="11"/>
+      <c r="L75" s="11"/>
+      <c r="M75" s="11"/>
+      <c r="N75" s="11"/>
+      <c r="O75" s="11"/>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76" s="11">
         <v>65</v>
       </c>
@@ -3100,15 +3825,30 @@
       <c r="C76" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="D76" s="11"/>
-      <c r="E76" s="11"/>
-      <c r="F76" s="11"/>
-      <c r="G76" s="11"/>
-      <c r="H76" s="15" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D76" s="11">
+        <v>9</v>
+      </c>
+      <c r="E76" s="11">
+        <v>9</v>
+      </c>
+      <c r="F76" s="11">
+        <v>9</v>
+      </c>
+      <c r="G76" s="11">
+        <v>10</v>
+      </c>
+      <c r="H76" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I76" s="11"/>
+      <c r="J76" s="11"/>
+      <c r="K76" s="11"/>
+      <c r="L76" s="11"/>
+      <c r="M76" s="11"/>
+      <c r="N76" s="11"/>
+      <c r="O76" s="11"/>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77" s="11">
         <v>66</v>
       </c>
@@ -3118,15 +3858,30 @@
       <c r="C77" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="D77" s="11"/>
-      <c r="E77" s="11"/>
-      <c r="F77" s="11"/>
-      <c r="G77" s="11"/>
-      <c r="H77" s="14" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D77" s="11">
+        <v>5</v>
+      </c>
+      <c r="E77" s="11">
+        <v>7</v>
+      </c>
+      <c r="F77" s="11">
+        <v>2</v>
+      </c>
+      <c r="G77" s="11">
+        <v>3</v>
+      </c>
+      <c r="H77" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I77" s="11"/>
+      <c r="J77" s="11"/>
+      <c r="K77" s="11"/>
+      <c r="L77" s="11"/>
+      <c r="M77" s="11"/>
+      <c r="N77" s="11"/>
+      <c r="O77" s="11"/>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78" s="11">
         <v>67</v>
       </c>
@@ -3136,15 +3891,30 @@
       <c r="C78" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="D78" s="11"/>
-      <c r="E78" s="11"/>
-      <c r="F78" s="11"/>
-      <c r="G78" s="11"/>
-      <c r="H78" s="14" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D78" s="11">
+        <v>5</v>
+      </c>
+      <c r="E78" s="11">
+        <v>16</v>
+      </c>
+      <c r="F78" s="11">
+        <v>5</v>
+      </c>
+      <c r="G78" s="11">
+        <v>4</v>
+      </c>
+      <c r="H78" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I78" s="11"/>
+      <c r="J78" s="11"/>
+      <c r="K78" s="11"/>
+      <c r="L78" s="11"/>
+      <c r="M78" s="11"/>
+      <c r="N78" s="11"/>
+      <c r="O78" s="11"/>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79" s="11">
         <v>68</v>
       </c>
@@ -3154,15 +3924,30 @@
       <c r="C79" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="D79" s="11"/>
-      <c r="E79" s="11"/>
-      <c r="F79" s="11"/>
-      <c r="G79" s="11"/>
-      <c r="H79" s="14" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D79" s="11">
+        <v>14</v>
+      </c>
+      <c r="E79" s="11">
+        <v>14</v>
+      </c>
+      <c r="F79" s="11">
+        <v>11</v>
+      </c>
+      <c r="G79" s="11">
+        <v>4</v>
+      </c>
+      <c r="H79" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I79" s="11"/>
+      <c r="J79" s="11"/>
+      <c r="K79" s="11"/>
+      <c r="L79" s="11"/>
+      <c r="M79" s="11"/>
+      <c r="N79" s="11"/>
+      <c r="O79" s="11"/>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80" s="11">
         <v>69</v>
       </c>
@@ -3172,15 +3957,30 @@
       <c r="C80" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="D80" s="11"/>
-      <c r="E80" s="11"/>
-      <c r="F80" s="11"/>
-      <c r="G80" s="11"/>
-      <c r="H80" s="16" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D80" s="11">
+        <v>11</v>
+      </c>
+      <c r="E80" s="11">
+        <v>3</v>
+      </c>
+      <c r="F80" s="11">
+        <v>12</v>
+      </c>
+      <c r="G80" s="11">
+        <v>4</v>
+      </c>
+      <c r="H80" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I80" s="11"/>
+      <c r="J80" s="11"/>
+      <c r="K80" s="11"/>
+      <c r="L80" s="11"/>
+      <c r="M80" s="11"/>
+      <c r="N80" s="11"/>
+      <c r="O80" s="11"/>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A81" s="11">
         <v>70</v>
       </c>
@@ -3190,15 +3990,30 @@
       <c r="C81" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="D81" s="11"/>
-      <c r="E81" s="11"/>
-      <c r="F81" s="11"/>
-      <c r="G81" s="11"/>
-      <c r="H81" s="14" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D81" s="11">
+        <v>4</v>
+      </c>
+      <c r="E81" s="11">
+        <v>13</v>
+      </c>
+      <c r="F81" s="11">
+        <v>12</v>
+      </c>
+      <c r="G81" s="11">
+        <v>15</v>
+      </c>
+      <c r="H81" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I81" s="11"/>
+      <c r="J81" s="11"/>
+      <c r="K81" s="11"/>
+      <c r="L81" s="11"/>
+      <c r="M81" s="11"/>
+      <c r="N81" s="11"/>
+      <c r="O81" s="11"/>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A82" s="11">
         <v>71</v>
       </c>
@@ -3208,15 +4023,30 @@
       <c r="C82" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="D82" s="11"/>
-      <c r="E82" s="11"/>
-      <c r="F82" s="11"/>
-      <c r="G82" s="11"/>
-      <c r="H82" s="14" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D82" s="11">
+        <v>12</v>
+      </c>
+      <c r="E82" s="11">
+        <v>16</v>
+      </c>
+      <c r="F82" s="11">
+        <v>3</v>
+      </c>
+      <c r="G82" s="11">
+        <v>3</v>
+      </c>
+      <c r="H82" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I82" s="11"/>
+      <c r="J82" s="11"/>
+      <c r="K82" s="11"/>
+      <c r="L82" s="11"/>
+      <c r="M82" s="11"/>
+      <c r="N82" s="11"/>
+      <c r="O82" s="11"/>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A83" s="11">
         <v>72</v>
       </c>
@@ -3226,15 +4056,30 @@
       <c r="C83" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="D83" s="11"/>
-      <c r="E83" s="11"/>
-      <c r="F83" s="11"/>
-      <c r="G83" s="11"/>
-      <c r="H83" s="14" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D83" s="11">
+        <v>5</v>
+      </c>
+      <c r="E83" s="11">
+        <v>15</v>
+      </c>
+      <c r="F83" s="11">
+        <v>6</v>
+      </c>
+      <c r="G83" s="11">
+        <v>7</v>
+      </c>
+      <c r="H83" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I83" s="11"/>
+      <c r="J83" s="11"/>
+      <c r="K83" s="11"/>
+      <c r="L83" s="11"/>
+      <c r="M83" s="11"/>
+      <c r="N83" s="11"/>
+      <c r="O83" s="11"/>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A84" s="11">
         <v>73</v>
       </c>
@@ -3244,15 +4089,30 @@
       <c r="C84" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="D84" s="11"/>
-      <c r="E84" s="11"/>
-      <c r="F84" s="11"/>
-      <c r="G84" s="11"/>
-      <c r="H84" s="14" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D84" s="11">
+        <v>6</v>
+      </c>
+      <c r="E84" s="11">
+        <v>3</v>
+      </c>
+      <c r="F84" s="11">
+        <v>3</v>
+      </c>
+      <c r="G84" s="11">
+        <v>5</v>
+      </c>
+      <c r="H84" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I84" s="11"/>
+      <c r="J84" s="11"/>
+      <c r="K84" s="11"/>
+      <c r="L84" s="11"/>
+      <c r="M84" s="11"/>
+      <c r="N84" s="11"/>
+      <c r="O84" s="11"/>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A85" s="11">
         <v>74</v>
       </c>
@@ -3262,15 +4122,30 @@
       <c r="C85" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="D85" s="11"/>
-      <c r="E85" s="11"/>
-      <c r="F85" s="11"/>
-      <c r="G85" s="11"/>
-      <c r="H85" s="14" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D85" s="11">
+        <v>3</v>
+      </c>
+      <c r="E85" s="11">
+        <v>5</v>
+      </c>
+      <c r="F85" s="11">
+        <v>7</v>
+      </c>
+      <c r="G85" s="11">
+        <v>7</v>
+      </c>
+      <c r="H85" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I85" s="11"/>
+      <c r="J85" s="11"/>
+      <c r="K85" s="11"/>
+      <c r="L85" s="11"/>
+      <c r="M85" s="11"/>
+      <c r="N85" s="11"/>
+      <c r="O85" s="11"/>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A86" s="11">
         <v>75</v>
       </c>
@@ -3280,15 +4155,30 @@
       <c r="C86" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="D86" s="11"/>
-      <c r="E86" s="11"/>
-      <c r="F86" s="11"/>
-      <c r="G86" s="11"/>
-      <c r="H86" s="14" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D86" s="11">
+        <v>4</v>
+      </c>
+      <c r="E86" s="11">
+        <v>14</v>
+      </c>
+      <c r="F86" s="11">
+        <v>7</v>
+      </c>
+      <c r="G86" s="11">
+        <v>9</v>
+      </c>
+      <c r="H86" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I86" s="11"/>
+      <c r="J86" s="11"/>
+      <c r="K86" s="11"/>
+      <c r="L86" s="11"/>
+      <c r="M86" s="11"/>
+      <c r="N86" s="11"/>
+      <c r="O86" s="11"/>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A87" s="11">
         <v>76</v>
       </c>
@@ -3298,13 +4188,28 @@
       <c r="C87" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="D87" s="11"/>
-      <c r="E87" s="11"/>
-      <c r="F87" s="11"/>
-      <c r="G87" s="11"/>
-      <c r="H87" s="14" t="s">
-        <v>247</v>
-      </c>
+      <c r="D87" s="11">
+        <v>6</v>
+      </c>
+      <c r="E87" s="11">
+        <v>16</v>
+      </c>
+      <c r="F87" s="11">
+        <v>15</v>
+      </c>
+      <c r="G87" s="11">
+        <v>7</v>
+      </c>
+      <c r="H87" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I87" s="11"/>
+      <c r="J87" s="11"/>
+      <c r="K87" s="11"/>
+      <c r="L87" s="11"/>
+      <c r="M87" s="11"/>
+      <c r="N87" s="11"/>
+      <c r="O87" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -3322,7 +4227,11 @@
     <mergeCell ref="F8:L8"/>
     <mergeCell ref="F5:L5"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="H12" r:id="rId1" xr:uid="{0D4A0A88-C4C3-4A84-B1FF-4D7548398E11}"/>
+    <hyperlink ref="H13:H87" r:id="rId2" display="parthlearner@gmail.com" xr:uid="{F126D5BB-0AA1-4A0F-87C6-0075DC7DA9BD}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>
--- a/dist/templates/SY1 Sem 4.xlsx
+++ b/dist/templates/SY1 Sem 4.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Old Downloads\Downloads\Automated Academic Report System\public\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Old Downloads\Downloads\WT DBMS CIE Project\Sample Excel Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CE73EDB-4A40-4C7D-9B9C-74509DAED30D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F921F143-CE21-4E54-8D07-2AA372271BE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" xr2:uid="{9825C9CF-F468-4764-ACEF-73A7F80F2223}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="249">
   <si>
     <t>Marathwada Mitra Mandal's</t>
   </si>
@@ -552,16 +552,244 @@
     <t>Email</t>
   </si>
   <si>
+    <t>tusharborate2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>sahilveer2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>vishweshbhilare2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>abhijitbedse2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>pravinambhore2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>avishkarpatil2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>neelkadam2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>kshitijbhate2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>maheshgaikwad2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>poojaumare2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>ayushchandekar2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>ritikmirase2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>vedantikaranaware2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>rugveddeshwant2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>swaradadeshpande2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>jahnavidhanapune2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>vaidehishinde2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>yugantvarekar2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>sajireedamle2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>yashmore2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>gayatridethe2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>srushtishewale2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>shravanipataskar2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>jidnyasapatil2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>ashutoshkulkarni2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>balrajrasal2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>anulaborse2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>gunajimohite2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>altamashmujawar2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>rajkumarmarathe2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>ashleshahumne2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>vikrantdagadkhair2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>jayantraut2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>abhijeethake2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>dnyaneshwarithorat2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>arihantborge2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>pruthvirajkokate2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>rajmohale2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>prathameshkirtane2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>sohambadarkhe2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>shivtejwagare2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>shubhamdorake2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>sanskrutigudhe2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>tanvikavate2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>sohamgawde2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>parthkshirsagar2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>anuragpatil2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>rohanmali2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>ishapatil2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>parthchaudhari2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>khileshchaudhari2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>yagneshpaliwal2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>animishdeo2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>asmitatawar2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>nirajfegade2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>janhavipatil2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>omchandurkar2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>atharvabhonde2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>srujalbhonde2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>parthtopale2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>niranjanmule2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>riteshmanthole2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>krishakulkarni2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>aayushjoshi2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>renukakulkarni2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>divyanshrai2024.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>sumitbhamare2025.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>vedantikamahadik2025.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>shreyashivade2025.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>dnyaneshwarithombal2025.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>diksharupnawar2025.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>shrutidalvi2025.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>tanvidongare2025.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>omkarkulkarni2025.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>prarthanakumbhar2025.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
+    <t>saniyashaikh2025.comp@mmcoe.edu.in</t>
+  </si>
+  <si>
     <t>IV</t>
-  </si>
-  <si>
-    <t>parthlearner@gmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm:ss"/>
+  </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -619,9 +847,8 @@
       <family val="1"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -641,7 +868,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -867,12 +1094,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -903,6 +1140,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1008,12 +1254,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1458,30 +1700,30 @@
   <cols>
     <col min="1" max="1" width="5.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.77734375" customWidth="1"/>
-    <col min="4" max="4" width="14.88671875" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="13.88671875" customWidth="1"/>
-    <col min="7" max="7" width="10.109375" customWidth="1"/>
-    <col min="8" max="8" width="41.33203125" customWidth="1"/>
+    <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="36.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="20.7" x14ac:dyDescent="0.35">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="22"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="25"/>
       <c r="N1" s="5"/>
       <c r="O1" s="5"/>
       <c r="P1" s="5"/>
@@ -1489,21 +1731,21 @@
       <c r="R1" s="5"/>
     </row>
     <row r="2" spans="1:18" ht="22.55" x14ac:dyDescent="0.35">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18"/>
-      <c r="M2" s="19"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+      <c r="M2" s="22"/>
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
       <c r="P2" s="6"/>
@@ -1511,21 +1753,21 @@
       <c r="R2" s="6"/>
     </row>
     <row r="3" spans="1:18" ht="16.3" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="15"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="16"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
+      <c r="L3" s="18"/>
+      <c r="M3" s="19"/>
       <c r="N3" s="7"/>
       <c r="O3" s="7"/>
       <c r="P3" s="7"/>
@@ -1554,21 +1796,21 @@
     </row>
     <row r="5" spans="1:18" ht="18.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
-      <c r="B5" s="31" t="s">
+      <c r="B5" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="32"/>
-      <c r="D5" s="33"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="36"/>
       <c r="E5" s="8"/>
-      <c r="F5" s="46" t="s">
+      <c r="F5" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="47"/>
-      <c r="H5" s="47"/>
-      <c r="I5" s="47"/>
-      <c r="J5" s="47"/>
-      <c r="K5" s="47"/>
-      <c r="L5" s="48"/>
+      <c r="G5" s="50"/>
+      <c r="H5" s="50"/>
+      <c r="I5" s="50"/>
+      <c r="J5" s="50"/>
+      <c r="K5" s="50"/>
+      <c r="L5" s="51"/>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1578,21 +1820,21 @@
     </row>
     <row r="6" spans="1:18" ht="18.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3"/>
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="35"/>
-      <c r="D6" s="36"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="39"/>
       <c r="E6" s="8"/>
-      <c r="F6" s="40" t="s">
+      <c r="F6" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="41"/>
-      <c r="K6" s="41"/>
-      <c r="L6" s="42"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="44"/>
+      <c r="K6" s="44"/>
+      <c r="L6" s="45"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
       <c r="P6" s="2"/>
@@ -1601,21 +1843,21 @@
     </row>
     <row r="7" spans="1:18" ht="18.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="28" t="s">
         <v>145</v>
       </c>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="29"/>
       <c r="E7" s="8"/>
-      <c r="F7" s="27" t="s">
+      <c r="F7" s="30" t="s">
         <v>146</v>
       </c>
-      <c r="G7" s="27"/>
-      <c r="H7" s="27"/>
-      <c r="I7" s="27"/>
-      <c r="J7" s="27"/>
-      <c r="K7" s="27"/>
-      <c r="L7" s="28"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="30"/>
+      <c r="K7" s="30"/>
+      <c r="L7" s="31"/>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
       <c r="P7" s="2"/>
@@ -1624,21 +1866,21 @@
     </row>
     <row r="8" spans="1:18" ht="18.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4"/>
-      <c r="B8" s="37" t="s">
+      <c r="B8" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="38"/>
-      <c r="D8" s="39"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="42"/>
       <c r="E8" s="8"/>
-      <c r="F8" s="43" t="s">
+      <c r="F8" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="G8" s="44"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="44"/>
-      <c r="K8" s="44"/>
-      <c r="L8" s="45"/>
+      <c r="G8" s="47"/>
+      <c r="H8" s="47"/>
+      <c r="I8" s="47"/>
+      <c r="J8" s="47"/>
+      <c r="K8" s="47"/>
+      <c r="L8" s="48"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1648,21 +1890,21 @@
     </row>
     <row r="9" spans="1:18" ht="18.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4"/>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="26" t="s">
         <v>144</v>
       </c>
-      <c r="C9" s="24"/>
-      <c r="D9" s="24"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
       <c r="E9" s="8"/>
-      <c r="F9" s="29" t="s">
-        <v>172</v>
-      </c>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29"/>
-      <c r="K9" s="29"/>
-      <c r="L9" s="30"/>
+      <c r="F9" s="32" t="s">
+        <v>248</v>
+      </c>
+      <c r="G9" s="32"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="32"/>
+      <c r="J9" s="32"/>
+      <c r="K9" s="32"/>
+      <c r="L9" s="33"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1695,13 +1937,6 @@
       <c r="H11" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="11">
@@ -1713,28 +1948,13 @@
       <c r="C12" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="11">
-        <v>16</v>
-      </c>
-      <c r="E12" s="11">
-        <v>10</v>
-      </c>
-      <c r="F12" s="11">
-        <v>9</v>
-      </c>
-      <c r="G12" s="11">
-        <v>10</v>
-      </c>
-      <c r="H12" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="11"/>
-      <c r="O12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="14" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="11">
@@ -1746,28 +1966,13 @@
       <c r="C13" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="11">
-        <v>16</v>
-      </c>
-      <c r="E13" s="11">
-        <v>11</v>
-      </c>
-      <c r="F13" s="11">
-        <v>14</v>
-      </c>
-      <c r="G13" s="11">
-        <v>13</v>
-      </c>
-      <c r="H13" s="49" t="s">
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="11"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="11">
@@ -1779,28 +1984,13 @@
       <c r="C14" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="11">
-        <v>16</v>
-      </c>
-      <c r="E14" s="11">
-        <v>15</v>
-      </c>
-      <c r="F14" s="11">
-        <v>13</v>
-      </c>
-      <c r="G14" s="11">
-        <v>16</v>
-      </c>
-      <c r="H14" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="11"/>
-      <c r="O14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="14" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="11">
@@ -1812,28 +2002,13 @@
       <c r="C15" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="11">
-        <v>7</v>
-      </c>
-      <c r="E15" s="11">
-        <v>5</v>
-      </c>
-      <c r="F15" s="11">
-        <v>6</v>
-      </c>
-      <c r="G15" s="11">
-        <v>9</v>
-      </c>
-      <c r="H15" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="14" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="11">
@@ -1845,30 +2020,15 @@
       <c r="C16" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="11">
-        <v>15</v>
-      </c>
-      <c r="E16" s="11">
-        <v>13</v>
-      </c>
-      <c r="F16" s="11">
-        <v>5</v>
-      </c>
-      <c r="G16" s="11">
-        <v>7</v>
-      </c>
-      <c r="H16" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
-      <c r="O16" s="11"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="14" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="11">
         <v>6</v>
       </c>
@@ -1878,30 +2038,15 @@
       <c r="C17" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="11">
-        <v>15</v>
-      </c>
-      <c r="E17" s="11">
-        <v>9</v>
-      </c>
-      <c r="F17" s="11">
-        <v>6</v>
-      </c>
-      <c r="G17" s="11">
-        <v>6</v>
-      </c>
-      <c r="H17" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="11"/>
-      <c r="O17" s="11"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="14" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="11">
         <v>7</v>
       </c>
@@ -1911,30 +2056,15 @@
       <c r="C18" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="11">
-        <v>14</v>
-      </c>
-      <c r="E18" s="11">
-        <v>14</v>
-      </c>
-      <c r="F18" s="11">
-        <v>6</v>
-      </c>
-      <c r="G18" s="11">
-        <v>9</v>
-      </c>
-      <c r="H18" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I18" s="11"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="11"/>
-      <c r="O18" s="11"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="14" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="11">
         <v>8</v>
       </c>
@@ -1944,30 +2074,15 @@
       <c r="C19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D19" s="11">
-        <v>13</v>
-      </c>
-      <c r="E19" s="11">
-        <v>12</v>
-      </c>
-      <c r="F19" s="11">
-        <v>3</v>
-      </c>
-      <c r="G19" s="11">
-        <v>3</v>
-      </c>
-      <c r="H19" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="11"/>
-      <c r="O19" s="11"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="14" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="11">
         <v>9</v>
       </c>
@@ -1977,30 +2092,15 @@
       <c r="C20" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D20" s="11">
-        <v>15</v>
-      </c>
-      <c r="E20" s="11">
-        <v>10</v>
-      </c>
-      <c r="F20" s="11">
-        <v>6</v>
-      </c>
-      <c r="G20" s="11">
-        <v>6</v>
-      </c>
-      <c r="H20" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I20" s="11"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="11"/>
-      <c r="N20" s="11"/>
-      <c r="O20" s="11"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="14" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="11">
         <v>10</v>
       </c>
@@ -2010,30 +2110,15 @@
       <c r="C21" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="11">
-        <v>7</v>
-      </c>
-      <c r="E21" s="11">
-        <v>7</v>
-      </c>
-      <c r="F21" s="11">
-        <v>3</v>
-      </c>
-      <c r="G21" s="11">
-        <v>4</v>
-      </c>
-      <c r="H21" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I21" s="11"/>
-      <c r="J21" s="11"/>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="11"/>
-      <c r="N21" s="11"/>
-      <c r="O21" s="11"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="14" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="11">
         <v>11</v>
       </c>
@@ -2043,30 +2128,15 @@
       <c r="C22" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="11">
-        <v>10</v>
-      </c>
-      <c r="E22" s="11">
-        <v>5</v>
-      </c>
-      <c r="F22" s="11">
-        <v>1</v>
-      </c>
-      <c r="G22" s="11">
-        <v>0</v>
-      </c>
-      <c r="H22" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I22" s="11"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="11"/>
-      <c r="O22" s="11"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="14" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="11">
         <v>12</v>
       </c>
@@ -2076,30 +2146,15 @@
       <c r="C23" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D23" s="11">
-        <v>11</v>
-      </c>
-      <c r="E23" s="11">
-        <v>8</v>
-      </c>
-      <c r="F23" s="11">
-        <v>8</v>
-      </c>
-      <c r="G23" s="11">
-        <v>2</v>
-      </c>
-      <c r="H23" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I23" s="11"/>
-      <c r="J23" s="11"/>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
-      <c r="N23" s="11"/>
-      <c r="O23" s="11"/>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="14" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="11">
         <v>13</v>
       </c>
@@ -2109,30 +2164,15 @@
       <c r="C24" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D24" s="11">
-        <v>12</v>
-      </c>
-      <c r="E24" s="11">
-        <v>15</v>
-      </c>
-      <c r="F24" s="11">
-        <v>14</v>
-      </c>
-      <c r="G24" s="11">
-        <v>16</v>
-      </c>
-      <c r="H24" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I24" s="11"/>
-      <c r="J24" s="11"/>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="11"/>
-      <c r="N24" s="11"/>
-      <c r="O24" s="11"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="14" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="11">
         <v>14</v>
       </c>
@@ -2142,30 +2182,15 @@
       <c r="C25" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D25" s="11">
-        <v>14</v>
-      </c>
-      <c r="E25" s="11">
-        <v>13</v>
-      </c>
-      <c r="F25" s="11">
-        <v>12</v>
-      </c>
-      <c r="G25" s="11">
-        <v>9</v>
-      </c>
-      <c r="H25" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I25" s="11"/>
-      <c r="J25" s="11"/>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="11"/>
-      <c r="N25" s="11"/>
-      <c r="O25" s="11"/>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="14" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="11">
         <v>15</v>
       </c>
@@ -2175,30 +2200,15 @@
       <c r="C26" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D26" s="11">
-        <v>10</v>
-      </c>
-      <c r="E26" s="11">
-        <v>13</v>
-      </c>
-      <c r="F26" s="11">
-        <v>6</v>
-      </c>
-      <c r="G26" s="11">
-        <v>13</v>
-      </c>
-      <c r="H26" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I26" s="11"/>
-      <c r="J26" s="11"/>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="11"/>
-      <c r="N26" s="11"/>
-      <c r="O26" s="11"/>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="14" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="11">
         <v>16</v>
       </c>
@@ -2208,30 +2218,15 @@
       <c r="C27" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="D27" s="11">
-        <v>14</v>
-      </c>
-      <c r="E27" s="11">
-        <v>12</v>
-      </c>
-      <c r="F27" s="11">
-        <v>6</v>
-      </c>
-      <c r="G27" s="11">
-        <v>9</v>
-      </c>
-      <c r="H27" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I27" s="11"/>
-      <c r="J27" s="11"/>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="11"/>
-      <c r="N27" s="11"/>
-      <c r="O27" s="11"/>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="14" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="11">
         <v>17</v>
       </c>
@@ -2241,30 +2236,15 @@
       <c r="C28" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D28" s="11">
-        <v>13</v>
-      </c>
-      <c r="E28" s="11">
-        <v>15</v>
-      </c>
-      <c r="F28" s="11">
-        <v>14</v>
-      </c>
-      <c r="G28" s="11">
-        <v>16</v>
-      </c>
-      <c r="H28" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I28" s="11"/>
-      <c r="J28" s="11"/>
-      <c r="K28" s="11"/>
-      <c r="L28" s="11"/>
-      <c r="M28" s="11"/>
-      <c r="N28" s="11"/>
-      <c r="O28" s="11"/>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="14" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="11">
         <v>18</v>
       </c>
@@ -2274,30 +2254,15 @@
       <c r="C29" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D29" s="11">
-        <v>13</v>
-      </c>
-      <c r="E29" s="11">
-        <v>13</v>
-      </c>
-      <c r="F29" s="11">
-        <v>15</v>
-      </c>
-      <c r="G29" s="11">
-        <v>12</v>
-      </c>
-      <c r="H29" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I29" s="11"/>
-      <c r="J29" s="11"/>
-      <c r="K29" s="11"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="11"/>
-      <c r="N29" s="11"/>
-      <c r="O29" s="11"/>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="14" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="11">
         <v>19</v>
       </c>
@@ -2307,30 +2272,15 @@
       <c r="C30" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="D30" s="11">
-        <v>14</v>
-      </c>
-      <c r="E30" s="11">
-        <v>16</v>
-      </c>
-      <c r="F30" s="11">
-        <v>14</v>
-      </c>
-      <c r="G30" s="11">
-        <v>12</v>
-      </c>
-      <c r="H30" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I30" s="11"/>
-      <c r="J30" s="11"/>
-      <c r="K30" s="11"/>
-      <c r="L30" s="11"/>
-      <c r="M30" s="11"/>
-      <c r="N30" s="11"/>
-      <c r="O30" s="11"/>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="14" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="11">
         <v>20</v>
       </c>
@@ -2340,30 +2290,15 @@
       <c r="C31" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="D31" s="11">
-        <v>5</v>
-      </c>
-      <c r="E31" s="11">
-        <v>6</v>
-      </c>
-      <c r="F31" s="11">
-        <v>6</v>
-      </c>
-      <c r="G31" s="11">
-        <v>7</v>
-      </c>
-      <c r="H31" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I31" s="11"/>
-      <c r="J31" s="11"/>
-      <c r="K31" s="11"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="11"/>
-      <c r="N31" s="11"/>
-      <c r="O31" s="11"/>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="14" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="11">
         <v>21</v>
       </c>
@@ -2373,30 +2308,15 @@
       <c r="C32" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="D32" s="11">
-        <v>11</v>
-      </c>
-      <c r="E32" s="11">
-        <v>9</v>
-      </c>
-      <c r="F32" s="11">
-        <v>7</v>
-      </c>
-      <c r="G32" s="11">
-        <v>8</v>
-      </c>
-      <c r="H32" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I32" s="11"/>
-      <c r="J32" s="11"/>
-      <c r="K32" s="11"/>
-      <c r="L32" s="11"/>
-      <c r="M32" s="11"/>
-      <c r="N32" s="11"/>
-      <c r="O32" s="11"/>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="14" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="11">
         <v>22</v>
       </c>
@@ -2406,30 +2326,15 @@
       <c r="C33" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="D33" s="11">
-        <v>8</v>
-      </c>
-      <c r="E33" s="11">
-        <v>7</v>
-      </c>
-      <c r="F33" s="11">
-        <v>6</v>
-      </c>
-      <c r="G33" s="11">
-        <v>11</v>
-      </c>
-      <c r="H33" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I33" s="11"/>
-      <c r="J33" s="11"/>
-      <c r="K33" s="11"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="11"/>
-      <c r="N33" s="11"/>
-      <c r="O33" s="11"/>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="11">
         <v>23</v>
       </c>
@@ -2439,30 +2344,15 @@
       <c r="C34" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="D34" s="11">
-        <v>16</v>
-      </c>
-      <c r="E34" s="11">
-        <v>16</v>
-      </c>
-      <c r="F34" s="11">
-        <v>14</v>
-      </c>
-      <c r="G34" s="11">
-        <v>14</v>
-      </c>
-      <c r="H34" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I34" s="11"/>
-      <c r="J34" s="11"/>
-      <c r="K34" s="11"/>
-      <c r="L34" s="11"/>
-      <c r="M34" s="11"/>
-      <c r="N34" s="11"/>
-      <c r="O34" s="11"/>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="14" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="11">
         <v>24</v>
       </c>
@@ -2472,30 +2362,15 @@
       <c r="C35" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="D35" s="11">
-        <v>16</v>
-      </c>
-      <c r="E35" s="11">
-        <v>16</v>
-      </c>
-      <c r="F35" s="11">
-        <v>15</v>
-      </c>
-      <c r="G35" s="11">
-        <v>13</v>
-      </c>
-      <c r="H35" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I35" s="11"/>
-      <c r="J35" s="11"/>
-      <c r="K35" s="11"/>
-      <c r="L35" s="11"/>
-      <c r="M35" s="11"/>
-      <c r="N35" s="11"/>
-      <c r="O35" s="11"/>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="14" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="11">
         <v>25</v>
       </c>
@@ -2505,30 +2380,15 @@
       <c r="C36" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="D36" s="11">
-        <v>13</v>
-      </c>
-      <c r="E36" s="11">
-        <v>14</v>
-      </c>
-      <c r="F36" s="11">
-        <v>7</v>
-      </c>
-      <c r="G36" s="11">
-        <v>12</v>
-      </c>
-      <c r="H36" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I36" s="11"/>
-      <c r="J36" s="11"/>
-      <c r="K36" s="11"/>
-      <c r="L36" s="11"/>
-      <c r="M36" s="11"/>
-      <c r="N36" s="11"/>
-      <c r="O36" s="11"/>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="14" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="11">
         <v>26</v>
       </c>
@@ -2538,30 +2398,15 @@
       <c r="C37" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="D37" s="11">
-        <v>9</v>
-      </c>
-      <c r="E37" s="11">
-        <v>4</v>
-      </c>
-      <c r="F37" s="11">
-        <v>6</v>
-      </c>
-      <c r="G37" s="11">
-        <v>11</v>
-      </c>
-      <c r="H37" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I37" s="11"/>
-      <c r="J37" s="11"/>
-      <c r="K37" s="11"/>
-      <c r="L37" s="11"/>
-      <c r="M37" s="11"/>
-      <c r="N37" s="11"/>
-      <c r="O37" s="11"/>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="14" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="11">
         <v>27</v>
       </c>
@@ -2571,30 +2416,15 @@
       <c r="C38" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="D38" s="11">
-        <v>15</v>
-      </c>
-      <c r="E38" s="11">
-        <v>11</v>
-      </c>
-      <c r="F38" s="11">
-        <v>5</v>
-      </c>
-      <c r="G38" s="11">
-        <v>7</v>
-      </c>
-      <c r="H38" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I38" s="11"/>
-      <c r="J38" s="11"/>
-      <c r="K38" s="11"/>
-      <c r="L38" s="11"/>
-      <c r="M38" s="11"/>
-      <c r="N38" s="11"/>
-      <c r="O38" s="11"/>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="14" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="11">
         <v>28</v>
       </c>
@@ -2604,30 +2434,15 @@
       <c r="C39" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="D39" s="11">
-        <v>15</v>
-      </c>
-      <c r="E39" s="11">
-        <v>15</v>
-      </c>
-      <c r="F39" s="11">
-        <v>9</v>
-      </c>
-      <c r="G39" s="11">
-        <v>7</v>
-      </c>
-      <c r="H39" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I39" s="11"/>
-      <c r="J39" s="11"/>
-      <c r="K39" s="11"/>
-      <c r="L39" s="11"/>
-      <c r="M39" s="11"/>
-      <c r="N39" s="11"/>
-      <c r="O39" s="11"/>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="11">
         <v>29</v>
       </c>
@@ -2637,30 +2452,15 @@
       <c r="C40" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="D40" s="11">
-        <v>16</v>
-      </c>
-      <c r="E40" s="11">
-        <v>10</v>
-      </c>
-      <c r="F40" s="11">
-        <v>11</v>
-      </c>
-      <c r="G40" s="11">
-        <v>14</v>
-      </c>
-      <c r="H40" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I40" s="11"/>
-      <c r="J40" s="11"/>
-      <c r="K40" s="11"/>
-      <c r="L40" s="11"/>
-      <c r="M40" s="11"/>
-      <c r="N40" s="11"/>
-      <c r="O40" s="11"/>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="14" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="11">
         <v>30</v>
       </c>
@@ -2670,30 +2470,15 @@
       <c r="C41" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="D41" s="11">
-        <v>14</v>
-      </c>
-      <c r="E41" s="11">
-        <v>14</v>
-      </c>
-      <c r="F41" s="11">
-        <v>10</v>
-      </c>
-      <c r="G41" s="11">
-        <v>11</v>
-      </c>
-      <c r="H41" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I41" s="11"/>
-      <c r="J41" s="11"/>
-      <c r="K41" s="11"/>
-      <c r="L41" s="11"/>
-      <c r="M41" s="11"/>
-      <c r="N41" s="11"/>
-      <c r="O41" s="11"/>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="14" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="11">
         <v>31</v>
       </c>
@@ -2703,30 +2488,15 @@
       <c r="C42" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="D42" s="11">
-        <v>15</v>
-      </c>
-      <c r="E42" s="11">
-        <v>14</v>
-      </c>
-      <c r="F42" s="11">
-        <v>7</v>
-      </c>
-      <c r="G42" s="11">
-        <v>8</v>
-      </c>
-      <c r="H42" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I42" s="11"/>
-      <c r="J42" s="11"/>
-      <c r="K42" s="11"/>
-      <c r="L42" s="11"/>
-      <c r="M42" s="11"/>
-      <c r="N42" s="11"/>
-      <c r="O42" s="11"/>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D42" s="11"/>
+      <c r="E42" s="11"/>
+      <c r="F42" s="11"/>
+      <c r="G42" s="11"/>
+      <c r="H42" s="14" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="11">
         <v>32</v>
       </c>
@@ -2736,30 +2506,15 @@
       <c r="C43" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="D43" s="11">
-        <v>8</v>
-      </c>
-      <c r="E43" s="11">
-        <v>9</v>
-      </c>
-      <c r="F43" s="11">
-        <v>6</v>
-      </c>
-      <c r="G43" s="11">
-        <v>2</v>
-      </c>
-      <c r="H43" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I43" s="11"/>
-      <c r="J43" s="11"/>
-      <c r="K43" s="11"/>
-      <c r="L43" s="11"/>
-      <c r="M43" s="11"/>
-      <c r="N43" s="11"/>
-      <c r="O43" s="11"/>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="14" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="11">
         <v>33</v>
       </c>
@@ -2769,30 +2524,15 @@
       <c r="C44" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="D44" s="11">
-        <v>11</v>
-      </c>
-      <c r="E44" s="11">
-        <v>11</v>
-      </c>
-      <c r="F44" s="11">
-        <v>10</v>
-      </c>
-      <c r="G44" s="11">
-        <v>8</v>
-      </c>
-      <c r="H44" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I44" s="11"/>
-      <c r="J44" s="11"/>
-      <c r="K44" s="11"/>
-      <c r="L44" s="11"/>
-      <c r="M44" s="11"/>
-      <c r="N44" s="11"/>
-      <c r="O44" s="11"/>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="11"/>
+      <c r="G44" s="11"/>
+      <c r="H44" s="14" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="11">
         <v>34</v>
       </c>
@@ -2802,30 +2542,15 @@
       <c r="C45" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="D45" s="11">
-        <v>16</v>
-      </c>
-      <c r="E45" s="11">
-        <v>11</v>
-      </c>
-      <c r="F45" s="11">
-        <v>10</v>
-      </c>
-      <c r="G45" s="11">
-        <v>13</v>
-      </c>
-      <c r="H45" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I45" s="11"/>
-      <c r="J45" s="11"/>
-      <c r="K45" s="11"/>
-      <c r="L45" s="11"/>
-      <c r="M45" s="11"/>
-      <c r="N45" s="11"/>
-      <c r="O45" s="11"/>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D45" s="11"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="11"/>
+      <c r="G45" s="11"/>
+      <c r="H45" s="14" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="11">
         <v>35</v>
       </c>
@@ -2835,30 +2560,15 @@
       <c r="C46" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="D46" s="11">
-        <v>14</v>
-      </c>
-      <c r="E46" s="11">
-        <v>13</v>
-      </c>
-      <c r="F46" s="11">
-        <v>8</v>
-      </c>
-      <c r="G46" s="11">
-        <v>10</v>
-      </c>
-      <c r="H46" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I46" s="11"/>
-      <c r="J46" s="11"/>
-      <c r="K46" s="11"/>
-      <c r="L46" s="11"/>
-      <c r="M46" s="11"/>
-      <c r="N46" s="11"/>
-      <c r="O46" s="11"/>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D46" s="11"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="11"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="14" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="11">
         <v>36</v>
       </c>
@@ -2868,30 +2578,15 @@
       <c r="C47" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="D47" s="11">
-        <v>8</v>
-      </c>
-      <c r="E47" s="11">
-        <v>14</v>
-      </c>
-      <c r="F47" s="11">
-        <v>8</v>
-      </c>
-      <c r="G47" s="11">
-        <v>6</v>
-      </c>
-      <c r="H47" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I47" s="11"/>
-      <c r="J47" s="11"/>
-      <c r="K47" s="11"/>
-      <c r="L47" s="11"/>
-      <c r="M47" s="11"/>
-      <c r="N47" s="11"/>
-      <c r="O47" s="11"/>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D47" s="11"/>
+      <c r="E47" s="11"/>
+      <c r="F47" s="11"/>
+      <c r="G47" s="11"/>
+      <c r="H47" s="14" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="11">
         <v>37</v>
       </c>
@@ -2901,30 +2596,15 @@
       <c r="C48" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="D48" s="11">
-        <v>12</v>
-      </c>
-      <c r="E48" s="11">
-        <v>14</v>
-      </c>
-      <c r="F48" s="11">
-        <v>5</v>
-      </c>
-      <c r="G48" s="11">
-        <v>7</v>
-      </c>
-      <c r="H48" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I48" s="11"/>
-      <c r="J48" s="11"/>
-      <c r="K48" s="11"/>
-      <c r="L48" s="11"/>
-      <c r="M48" s="11"/>
-      <c r="N48" s="11"/>
-      <c r="O48" s="11"/>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D48" s="11"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="11"/>
+      <c r="G48" s="11"/>
+      <c r="H48" s="14" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="11">
         <v>38</v>
       </c>
@@ -2934,30 +2614,15 @@
       <c r="C49" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="D49" s="11">
-        <v>13</v>
-      </c>
-      <c r="E49" s="11">
-        <v>16</v>
-      </c>
-      <c r="F49" s="11">
-        <v>10</v>
-      </c>
-      <c r="G49" s="11">
-        <v>13</v>
-      </c>
-      <c r="H49" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I49" s="11"/>
-      <c r="J49" s="11"/>
-      <c r="K49" s="11"/>
-      <c r="L49" s="11"/>
-      <c r="M49" s="11"/>
-      <c r="N49" s="11"/>
-      <c r="O49" s="11"/>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D49" s="11"/>
+      <c r="E49" s="11"/>
+      <c r="F49" s="11"/>
+      <c r="G49" s="11"/>
+      <c r="H49" s="14" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="11">
         <v>39</v>
       </c>
@@ -2967,30 +2632,15 @@
       <c r="C50" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="D50" s="11">
-        <v>0</v>
-      </c>
-      <c r="E50" s="11">
-        <v>8</v>
-      </c>
-      <c r="F50" s="11">
-        <v>0</v>
-      </c>
-      <c r="G50" s="11">
-        <v>0</v>
-      </c>
-      <c r="H50" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I50" s="11"/>
-      <c r="J50" s="11"/>
-      <c r="K50" s="11"/>
-      <c r="L50" s="11"/>
-      <c r="M50" s="11"/>
-      <c r="N50" s="11"/>
-      <c r="O50" s="11"/>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D50" s="11"/>
+      <c r="E50" s="11"/>
+      <c r="F50" s="11"/>
+      <c r="G50" s="11"/>
+      <c r="H50" s="14" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="11">
         <v>40</v>
       </c>
@@ -3000,30 +2650,15 @@
       <c r="C51" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="D51" s="11">
-        <v>11</v>
-      </c>
-      <c r="E51" s="11">
-        <v>12</v>
-      </c>
-      <c r="F51" s="11">
-        <v>8</v>
-      </c>
-      <c r="G51" s="11">
-        <v>7</v>
-      </c>
-      <c r="H51" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I51" s="11"/>
-      <c r="J51" s="11"/>
-      <c r="K51" s="11"/>
-      <c r="L51" s="11"/>
-      <c r="M51" s="11"/>
-      <c r="N51" s="11"/>
-      <c r="O51" s="11"/>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D51" s="11"/>
+      <c r="E51" s="11"/>
+      <c r="F51" s="11"/>
+      <c r="G51" s="11"/>
+      <c r="H51" s="14" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="11">
         <v>41</v>
       </c>
@@ -3033,30 +2668,15 @@
       <c r="C52" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="D52" s="11">
-        <v>8</v>
-      </c>
-      <c r="E52" s="11">
-        <v>6</v>
-      </c>
-      <c r="F52" s="11">
-        <v>4</v>
-      </c>
-      <c r="G52" s="11">
-        <v>13</v>
-      </c>
-      <c r="H52" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I52" s="11"/>
-      <c r="J52" s="11"/>
-      <c r="K52" s="11"/>
-      <c r="L52" s="11"/>
-      <c r="M52" s="11"/>
-      <c r="N52" s="11"/>
-      <c r="O52" s="11"/>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D52" s="11"/>
+      <c r="E52" s="11"/>
+      <c r="F52" s="11"/>
+      <c r="G52" s="11"/>
+      <c r="H52" s="14" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="11">
         <v>42</v>
       </c>
@@ -3066,30 +2686,15 @@
       <c r="C53" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="D53" s="11">
-        <v>10</v>
-      </c>
-      <c r="E53" s="11">
-        <v>15</v>
-      </c>
-      <c r="F53" s="11">
-        <v>6</v>
-      </c>
-      <c r="G53" s="11">
-        <v>9</v>
-      </c>
-      <c r="H53" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I53" s="11"/>
-      <c r="J53" s="11"/>
-      <c r="K53" s="11"/>
-      <c r="L53" s="11"/>
-      <c r="M53" s="11"/>
-      <c r="N53" s="11"/>
-      <c r="O53" s="11"/>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D53" s="11"/>
+      <c r="E53" s="11"/>
+      <c r="F53" s="11"/>
+      <c r="G53" s="11"/>
+      <c r="H53" s="14" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="11">
         <v>43</v>
       </c>
@@ -3099,30 +2704,15 @@
       <c r="C54" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="D54" s="11">
-        <v>10</v>
-      </c>
-      <c r="E54" s="11">
-        <v>12</v>
-      </c>
-      <c r="F54" s="11">
-        <v>10</v>
-      </c>
-      <c r="G54" s="11">
-        <v>13</v>
-      </c>
-      <c r="H54" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I54" s="11"/>
-      <c r="J54" s="11"/>
-      <c r="K54" s="11"/>
-      <c r="L54" s="11"/>
-      <c r="M54" s="11"/>
-      <c r="N54" s="11"/>
-      <c r="O54" s="11"/>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D54" s="11"/>
+      <c r="E54" s="11"/>
+      <c r="F54" s="11"/>
+      <c r="G54" s="11"/>
+      <c r="H54" s="14" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="11">
         <v>44</v>
       </c>
@@ -3132,30 +2722,15 @@
       <c r="C55" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="D55" s="11">
-        <v>0</v>
-      </c>
-      <c r="E55" s="11">
-        <v>0</v>
-      </c>
-      <c r="F55" s="11">
-        <v>0</v>
-      </c>
-      <c r="G55" s="11">
-        <v>1</v>
-      </c>
-      <c r="H55" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I55" s="11"/>
-      <c r="J55" s="11"/>
-      <c r="K55" s="11"/>
-      <c r="L55" s="11"/>
-      <c r="M55" s="11"/>
-      <c r="N55" s="11"/>
-      <c r="O55" s="11"/>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D55" s="11"/>
+      <c r="E55" s="11"/>
+      <c r="F55" s="11"/>
+      <c r="G55" s="11"/>
+      <c r="H55" s="14" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="11">
         <v>45</v>
       </c>
@@ -3165,30 +2740,15 @@
       <c r="C56" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="D56" s="11">
-        <v>13</v>
-      </c>
-      <c r="E56" s="11">
-        <v>8</v>
-      </c>
-      <c r="F56" s="11">
-        <v>5</v>
-      </c>
-      <c r="G56" s="11">
-        <v>14</v>
-      </c>
-      <c r="H56" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I56" s="11"/>
-      <c r="J56" s="11"/>
-      <c r="K56" s="11"/>
-      <c r="L56" s="11"/>
-      <c r="M56" s="11"/>
-      <c r="N56" s="11"/>
-      <c r="O56" s="11"/>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D56" s="11"/>
+      <c r="E56" s="11"/>
+      <c r="F56" s="11"/>
+      <c r="G56" s="11"/>
+      <c r="H56" s="14" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="11">
         <v>46</v>
       </c>
@@ -3198,30 +2758,15 @@
       <c r="C57" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="D57" s="11">
-        <v>13</v>
-      </c>
-      <c r="E57" s="11">
-        <v>14</v>
-      </c>
-      <c r="F57" s="11">
-        <v>7</v>
-      </c>
-      <c r="G57" s="11">
-        <v>6</v>
-      </c>
-      <c r="H57" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I57" s="11"/>
-      <c r="J57" s="11"/>
-      <c r="K57" s="11"/>
-      <c r="L57" s="11"/>
-      <c r="M57" s="11"/>
-      <c r="N57" s="11"/>
-      <c r="O57" s="11"/>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D57" s="11"/>
+      <c r="E57" s="11"/>
+      <c r="F57" s="11"/>
+      <c r="G57" s="11"/>
+      <c r="H57" s="14" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="11">
         <v>47</v>
       </c>
@@ -3231,30 +2776,15 @@
       <c r="C58" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="D58" s="11">
-        <v>16</v>
-      </c>
-      <c r="E58" s="11">
-        <v>12</v>
-      </c>
-      <c r="F58" s="11">
-        <v>6</v>
-      </c>
-      <c r="G58" s="11">
-        <v>9</v>
-      </c>
-      <c r="H58" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I58" s="11"/>
-      <c r="J58" s="11"/>
-      <c r="K58" s="11"/>
-      <c r="L58" s="11"/>
-      <c r="M58" s="11"/>
-      <c r="N58" s="11"/>
-      <c r="O58" s="11"/>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D58" s="11"/>
+      <c r="E58" s="11"/>
+      <c r="F58" s="11"/>
+      <c r="G58" s="11"/>
+      <c r="H58" s="14" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="11">
         <v>48</v>
       </c>
@@ -3264,30 +2794,15 @@
       <c r="C59" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="D59" s="11">
-        <v>10</v>
-      </c>
-      <c r="E59" s="11">
-        <v>4</v>
-      </c>
-      <c r="F59" s="11">
-        <v>1</v>
-      </c>
-      <c r="G59" s="11">
-        <v>12</v>
-      </c>
-      <c r="H59" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I59" s="11"/>
-      <c r="J59" s="11"/>
-      <c r="K59" s="11"/>
-      <c r="L59" s="11"/>
-      <c r="M59" s="11"/>
-      <c r="N59" s="11"/>
-      <c r="O59" s="11"/>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D59" s="11"/>
+      <c r="E59" s="11"/>
+      <c r="F59" s="11"/>
+      <c r="G59" s="11"/>
+      <c r="H59" s="14" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="11">
         <v>49</v>
       </c>
@@ -3297,30 +2812,15 @@
       <c r="C60" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="D60" s="11">
-        <v>12</v>
-      </c>
-      <c r="E60" s="11">
-        <v>14</v>
-      </c>
-      <c r="F60" s="11">
-        <v>14</v>
-      </c>
-      <c r="G60" s="11">
-        <v>9</v>
-      </c>
-      <c r="H60" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I60" s="11"/>
-      <c r="J60" s="11"/>
-      <c r="K60" s="11"/>
-      <c r="L60" s="11"/>
-      <c r="M60" s="11"/>
-      <c r="N60" s="11"/>
-      <c r="O60" s="11"/>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D60" s="11"/>
+      <c r="E60" s="11"/>
+      <c r="F60" s="11"/>
+      <c r="G60" s="11"/>
+      <c r="H60" s="14" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="11">
         <v>50</v>
       </c>
@@ -3330,30 +2830,15 @@
       <c r="C61" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="D61" s="11">
-        <v>16</v>
-      </c>
-      <c r="E61" s="11">
-        <v>13</v>
-      </c>
-      <c r="F61" s="11">
-        <v>11</v>
-      </c>
-      <c r="G61" s="11">
-        <v>16</v>
-      </c>
-      <c r="H61" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I61" s="11"/>
-      <c r="J61" s="11"/>
-      <c r="K61" s="11"/>
-      <c r="L61" s="11"/>
-      <c r="M61" s="11"/>
-      <c r="N61" s="11"/>
-      <c r="O61" s="11"/>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D61" s="11"/>
+      <c r="E61" s="11"/>
+      <c r="F61" s="11"/>
+      <c r="G61" s="11"/>
+      <c r="H61" s="14" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="11">
         <v>51</v>
       </c>
@@ -3363,30 +2848,15 @@
       <c r="C62" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="D62" s="11">
-        <v>14</v>
-      </c>
-      <c r="E62" s="11">
-        <v>12</v>
-      </c>
-      <c r="F62" s="11">
-        <v>14</v>
-      </c>
-      <c r="G62" s="11">
-        <v>14</v>
-      </c>
-      <c r="H62" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I62" s="11"/>
-      <c r="J62" s="11"/>
-      <c r="K62" s="11"/>
-      <c r="L62" s="11"/>
-      <c r="M62" s="11"/>
-      <c r="N62" s="11"/>
-      <c r="O62" s="11"/>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D62" s="11"/>
+      <c r="E62" s="11"/>
+      <c r="F62" s="11"/>
+      <c r="G62" s="11"/>
+      <c r="H62" s="14" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="11">
         <v>52</v>
       </c>
@@ -3396,30 +2866,15 @@
       <c r="C63" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="D63" s="11">
-        <v>15</v>
-      </c>
-      <c r="E63" s="11">
-        <v>9</v>
-      </c>
-      <c r="F63" s="11">
-        <v>16</v>
-      </c>
-      <c r="G63" s="11">
-        <v>11</v>
-      </c>
-      <c r="H63" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I63" s="11"/>
-      <c r="J63" s="11"/>
-      <c r="K63" s="11"/>
-      <c r="L63" s="11"/>
-      <c r="M63" s="11"/>
-      <c r="N63" s="11"/>
-      <c r="O63" s="11"/>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D63" s="11"/>
+      <c r="E63" s="11"/>
+      <c r="F63" s="11"/>
+      <c r="G63" s="11"/>
+      <c r="H63" s="14" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="11">
         <v>53</v>
       </c>
@@ -3429,30 +2884,15 @@
       <c r="C64" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="D64" s="11">
-        <v>14</v>
-      </c>
-      <c r="E64" s="11">
-        <v>16</v>
-      </c>
-      <c r="F64" s="11">
-        <v>4</v>
-      </c>
-      <c r="G64" s="11">
-        <v>11</v>
-      </c>
-      <c r="H64" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I64" s="11"/>
-      <c r="J64" s="11"/>
-      <c r="K64" s="11"/>
-      <c r="L64" s="11"/>
-      <c r="M64" s="11"/>
-      <c r="N64" s="11"/>
-      <c r="O64" s="11"/>
-    </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D64" s="11"/>
+      <c r="E64" s="11"/>
+      <c r="F64" s="11"/>
+      <c r="G64" s="11"/>
+      <c r="H64" s="14" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="11">
         <v>54</v>
       </c>
@@ -3462,30 +2902,15 @@
       <c r="C65" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="D65" s="11">
-        <v>15</v>
-      </c>
-      <c r="E65" s="11">
-        <v>13</v>
-      </c>
-      <c r="F65" s="11">
-        <v>14</v>
-      </c>
-      <c r="G65" s="11">
-        <v>9</v>
-      </c>
-      <c r="H65" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I65" s="11"/>
-      <c r="J65" s="11"/>
-      <c r="K65" s="11"/>
-      <c r="L65" s="11"/>
-      <c r="M65" s="11"/>
-      <c r="N65" s="11"/>
-      <c r="O65" s="11"/>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D65" s="11"/>
+      <c r="E65" s="11"/>
+      <c r="F65" s="11"/>
+      <c r="G65" s="11"/>
+      <c r="H65" s="14" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="11">
         <v>55</v>
       </c>
@@ -3495,30 +2920,15 @@
       <c r="C66" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D66" s="11">
-        <v>11</v>
-      </c>
-      <c r="E66" s="11">
-        <v>10</v>
-      </c>
-      <c r="F66" s="11">
-        <v>7</v>
-      </c>
-      <c r="G66" s="11">
-        <v>15</v>
-      </c>
-      <c r="H66" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I66" s="11"/>
-      <c r="J66" s="11"/>
-      <c r="K66" s="11"/>
-      <c r="L66" s="11"/>
-      <c r="M66" s="11"/>
-      <c r="N66" s="11"/>
-      <c r="O66" s="11"/>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D66" s="11"/>
+      <c r="E66" s="11"/>
+      <c r="F66" s="11"/>
+      <c r="G66" s="11"/>
+      <c r="H66" s="14" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="11">
         <v>56</v>
       </c>
@@ -3528,30 +2938,15 @@
       <c r="C67" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="D67" s="11">
-        <v>12</v>
-      </c>
-      <c r="E67" s="11">
-        <v>14</v>
-      </c>
-      <c r="F67" s="11">
-        <v>12</v>
-      </c>
-      <c r="G67" s="11">
-        <v>14</v>
-      </c>
-      <c r="H67" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I67" s="11"/>
-      <c r="J67" s="11"/>
-      <c r="K67" s="11"/>
-      <c r="L67" s="11"/>
-      <c r="M67" s="11"/>
-      <c r="N67" s="11"/>
-      <c r="O67" s="11"/>
-    </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D67" s="11"/>
+      <c r="E67" s="11"/>
+      <c r="F67" s="11"/>
+      <c r="G67" s="11"/>
+      <c r="H67" s="14" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="11">
         <v>57</v>
       </c>
@@ -3561,30 +2956,15 @@
       <c r="C68" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="D68" s="11">
-        <v>8</v>
-      </c>
-      <c r="E68" s="11">
-        <v>13</v>
-      </c>
-      <c r="F68" s="11">
-        <v>5</v>
-      </c>
-      <c r="G68" s="11">
-        <v>13</v>
-      </c>
-      <c r="H68" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I68" s="11"/>
-      <c r="J68" s="11"/>
-      <c r="K68" s="11"/>
-      <c r="L68" s="11"/>
-      <c r="M68" s="11"/>
-      <c r="N68" s="11"/>
-      <c r="O68" s="11"/>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D68" s="11"/>
+      <c r="E68" s="11"/>
+      <c r="F68" s="11"/>
+      <c r="G68" s="11"/>
+      <c r="H68" s="14" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="11">
         <v>58</v>
       </c>
@@ -3594,30 +2974,15 @@
       <c r="C69" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D69" s="11">
-        <v>9</v>
-      </c>
-      <c r="E69" s="11">
-        <v>12</v>
-      </c>
-      <c r="F69" s="11">
-        <v>3</v>
-      </c>
-      <c r="G69" s="11">
-        <v>5</v>
-      </c>
-      <c r="H69" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I69" s="11"/>
-      <c r="J69" s="11"/>
-      <c r="K69" s="11"/>
-      <c r="L69" s="11"/>
-      <c r="M69" s="11"/>
-      <c r="N69" s="11"/>
-      <c r="O69" s="11"/>
-    </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D69" s="11"/>
+      <c r="E69" s="11"/>
+      <c r="F69" s="11"/>
+      <c r="G69" s="11"/>
+      <c r="H69" s="14" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="11">
         <v>59</v>
       </c>
@@ -3627,30 +2992,15 @@
       <c r="C70" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="D70" s="11">
-        <v>6</v>
-      </c>
-      <c r="E70" s="11">
-        <v>7</v>
-      </c>
-      <c r="F70" s="11">
-        <v>4</v>
-      </c>
-      <c r="G70" s="11">
-        <v>8</v>
-      </c>
-      <c r="H70" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I70" s="11"/>
-      <c r="J70" s="11"/>
-      <c r="K70" s="11"/>
-      <c r="L70" s="11"/>
-      <c r="M70" s="11"/>
-      <c r="N70" s="11"/>
-      <c r="O70" s="11"/>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D70" s="11"/>
+      <c r="E70" s="11"/>
+      <c r="F70" s="11"/>
+      <c r="G70" s="11"/>
+      <c r="H70" s="14" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="11">
         <v>60</v>
       </c>
@@ -3660,30 +3010,15 @@
       <c r="C71" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="D71" s="11">
-        <v>10</v>
-      </c>
-      <c r="E71" s="11">
-        <v>9</v>
-      </c>
-      <c r="F71" s="11">
-        <v>4</v>
-      </c>
-      <c r="G71" s="11">
-        <v>13</v>
-      </c>
-      <c r="H71" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I71" s="11"/>
-      <c r="J71" s="11"/>
-      <c r="K71" s="11"/>
-      <c r="L71" s="11"/>
-      <c r="M71" s="11"/>
-      <c r="N71" s="11"/>
-      <c r="O71" s="11"/>
-    </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D71" s="11"/>
+      <c r="E71" s="11"/>
+      <c r="F71" s="11"/>
+      <c r="G71" s="11"/>
+      <c r="H71" s="14" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="11">
         <v>61</v>
       </c>
@@ -3693,30 +3028,15 @@
       <c r="C72" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="D72" s="11">
-        <v>13</v>
-      </c>
-      <c r="E72" s="11">
-        <v>11</v>
-      </c>
-      <c r="F72" s="11">
-        <v>2</v>
-      </c>
-      <c r="G72" s="11">
-        <v>11</v>
-      </c>
-      <c r="H72" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I72" s="11"/>
-      <c r="J72" s="11"/>
-      <c r="K72" s="11"/>
-      <c r="L72" s="11"/>
-      <c r="M72" s="11"/>
-      <c r="N72" s="11"/>
-      <c r="O72" s="11"/>
-    </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D72" s="11"/>
+      <c r="E72" s="11"/>
+      <c r="F72" s="11"/>
+      <c r="G72" s="11"/>
+      <c r="H72" s="14" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="11">
         <v>62</v>
       </c>
@@ -3726,30 +3046,15 @@
       <c r="C73" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="D73" s="11">
-        <v>11</v>
-      </c>
-      <c r="E73" s="11">
-        <v>9</v>
-      </c>
-      <c r="F73" s="11">
-        <v>13</v>
-      </c>
-      <c r="G73" s="11">
-        <v>14</v>
-      </c>
-      <c r="H73" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I73" s="11"/>
-      <c r="J73" s="11"/>
-      <c r="K73" s="11"/>
-      <c r="L73" s="11"/>
-      <c r="M73" s="11"/>
-      <c r="N73" s="11"/>
-      <c r="O73" s="11"/>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D73" s="11"/>
+      <c r="E73" s="11"/>
+      <c r="F73" s="11"/>
+      <c r="G73" s="11"/>
+      <c r="H73" s="14" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="11">
         <v>63</v>
       </c>
@@ -3759,30 +3064,15 @@
       <c r="C74" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="D74" s="11">
-        <v>13</v>
-      </c>
-      <c r="E74" s="11">
-        <v>13</v>
-      </c>
-      <c r="F74" s="11">
-        <v>16</v>
-      </c>
-      <c r="G74" s="11">
-        <v>12</v>
-      </c>
-      <c r="H74" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I74" s="11"/>
-      <c r="J74" s="11"/>
-      <c r="K74" s="11"/>
-      <c r="L74" s="11"/>
-      <c r="M74" s="11"/>
-      <c r="N74" s="11"/>
-      <c r="O74" s="11"/>
-    </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D74" s="11"/>
+      <c r="E74" s="11"/>
+      <c r="F74" s="11"/>
+      <c r="G74" s="11"/>
+      <c r="H74" s="14" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="11">
         <v>64</v>
       </c>
@@ -3792,30 +3082,15 @@
       <c r="C75" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="D75" s="11">
-        <v>10</v>
-      </c>
-      <c r="E75" s="11">
-        <v>14</v>
-      </c>
-      <c r="F75" s="11">
-        <v>7</v>
-      </c>
-      <c r="G75" s="11">
-        <v>7</v>
-      </c>
-      <c r="H75" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I75" s="11"/>
-      <c r="J75" s="11"/>
-      <c r="K75" s="11"/>
-      <c r="L75" s="11"/>
-      <c r="M75" s="11"/>
-      <c r="N75" s="11"/>
-      <c r="O75" s="11"/>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D75" s="11"/>
+      <c r="E75" s="11"/>
+      <c r="F75" s="11"/>
+      <c r="G75" s="11"/>
+      <c r="H75" s="14" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="11">
         <v>65</v>
       </c>
@@ -3825,30 +3100,15 @@
       <c r="C76" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="D76" s="11">
-        <v>9</v>
-      </c>
-      <c r="E76" s="11">
-        <v>9</v>
-      </c>
-      <c r="F76" s="11">
-        <v>9</v>
-      </c>
-      <c r="G76" s="11">
-        <v>10</v>
-      </c>
-      <c r="H76" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I76" s="11"/>
-      <c r="J76" s="11"/>
-      <c r="K76" s="11"/>
-      <c r="L76" s="11"/>
-      <c r="M76" s="11"/>
-      <c r="N76" s="11"/>
-      <c r="O76" s="11"/>
-    </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D76" s="11"/>
+      <c r="E76" s="11"/>
+      <c r="F76" s="11"/>
+      <c r="G76" s="11"/>
+      <c r="H76" s="15" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="11">
         <v>66</v>
       </c>
@@ -3858,30 +3118,15 @@
       <c r="C77" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="D77" s="11">
-        <v>5</v>
-      </c>
-      <c r="E77" s="11">
-        <v>7</v>
-      </c>
-      <c r="F77" s="11">
-        <v>2</v>
-      </c>
-      <c r="G77" s="11">
-        <v>3</v>
-      </c>
-      <c r="H77" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I77" s="11"/>
-      <c r="J77" s="11"/>
-      <c r="K77" s="11"/>
-      <c r="L77" s="11"/>
-      <c r="M77" s="11"/>
-      <c r="N77" s="11"/>
-      <c r="O77" s="11"/>
-    </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D77" s="11"/>
+      <c r="E77" s="11"/>
+      <c r="F77" s="11"/>
+      <c r="G77" s="11"/>
+      <c r="H77" s="14" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="11">
         <v>67</v>
       </c>
@@ -3891,30 +3136,15 @@
       <c r="C78" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="D78" s="11">
-        <v>5</v>
-      </c>
-      <c r="E78" s="11">
-        <v>16</v>
-      </c>
-      <c r="F78" s="11">
-        <v>5</v>
-      </c>
-      <c r="G78" s="11">
-        <v>4</v>
-      </c>
-      <c r="H78" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I78" s="11"/>
-      <c r="J78" s="11"/>
-      <c r="K78" s="11"/>
-      <c r="L78" s="11"/>
-      <c r="M78" s="11"/>
-      <c r="N78" s="11"/>
-      <c r="O78" s="11"/>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D78" s="11"/>
+      <c r="E78" s="11"/>
+      <c r="F78" s="11"/>
+      <c r="G78" s="11"/>
+      <c r="H78" s="14" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="11">
         <v>68</v>
       </c>
@@ -3924,30 +3154,15 @@
       <c r="C79" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="D79" s="11">
-        <v>14</v>
-      </c>
-      <c r="E79" s="11">
-        <v>14</v>
-      </c>
-      <c r="F79" s="11">
-        <v>11</v>
-      </c>
-      <c r="G79" s="11">
-        <v>4</v>
-      </c>
-      <c r="H79" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I79" s="11"/>
-      <c r="J79" s="11"/>
-      <c r="K79" s="11"/>
-      <c r="L79" s="11"/>
-      <c r="M79" s="11"/>
-      <c r="N79" s="11"/>
-      <c r="O79" s="11"/>
-    </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D79" s="11"/>
+      <c r="E79" s="11"/>
+      <c r="F79" s="11"/>
+      <c r="G79" s="11"/>
+      <c r="H79" s="14" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="11">
         <v>69</v>
       </c>
@@ -3957,30 +3172,15 @@
       <c r="C80" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="D80" s="11">
-        <v>11</v>
-      </c>
-      <c r="E80" s="11">
-        <v>3</v>
-      </c>
-      <c r="F80" s="11">
-        <v>12</v>
-      </c>
-      <c r="G80" s="11">
-        <v>4</v>
-      </c>
-      <c r="H80" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I80" s="11"/>
-      <c r="J80" s="11"/>
-      <c r="K80" s="11"/>
-      <c r="L80" s="11"/>
-      <c r="M80" s="11"/>
-      <c r="N80" s="11"/>
-      <c r="O80" s="11"/>
-    </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D80" s="11"/>
+      <c r="E80" s="11"/>
+      <c r="F80" s="11"/>
+      <c r="G80" s="11"/>
+      <c r="H80" s="16" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="11">
         <v>70</v>
       </c>
@@ -3990,30 +3190,15 @@
       <c r="C81" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="D81" s="11">
-        <v>4</v>
-      </c>
-      <c r="E81" s="11">
-        <v>13</v>
-      </c>
-      <c r="F81" s="11">
-        <v>12</v>
-      </c>
-      <c r="G81" s="11">
-        <v>15</v>
-      </c>
-      <c r="H81" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I81" s="11"/>
-      <c r="J81" s="11"/>
-      <c r="K81" s="11"/>
-      <c r="L81" s="11"/>
-      <c r="M81" s="11"/>
-      <c r="N81" s="11"/>
-      <c r="O81" s="11"/>
-    </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D81" s="11"/>
+      <c r="E81" s="11"/>
+      <c r="F81" s="11"/>
+      <c r="G81" s="11"/>
+      <c r="H81" s="14" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="11">
         <v>71</v>
       </c>
@@ -4023,30 +3208,15 @@
       <c r="C82" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="D82" s="11">
-        <v>12</v>
-      </c>
-      <c r="E82" s="11">
-        <v>16</v>
-      </c>
-      <c r="F82" s="11">
-        <v>3</v>
-      </c>
-      <c r="G82" s="11">
-        <v>3</v>
-      </c>
-      <c r="H82" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I82" s="11"/>
-      <c r="J82" s="11"/>
-      <c r="K82" s="11"/>
-      <c r="L82" s="11"/>
-      <c r="M82" s="11"/>
-      <c r="N82" s="11"/>
-      <c r="O82" s="11"/>
-    </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D82" s="11"/>
+      <c r="E82" s="11"/>
+      <c r="F82" s="11"/>
+      <c r="G82" s="11"/>
+      <c r="H82" s="14" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="11">
         <v>72</v>
       </c>
@@ -4056,30 +3226,15 @@
       <c r="C83" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="D83" s="11">
-        <v>5</v>
-      </c>
-      <c r="E83" s="11">
-        <v>15</v>
-      </c>
-      <c r="F83" s="11">
-        <v>6</v>
-      </c>
-      <c r="G83" s="11">
-        <v>7</v>
-      </c>
-      <c r="H83" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I83" s="11"/>
-      <c r="J83" s="11"/>
-      <c r="K83" s="11"/>
-      <c r="L83" s="11"/>
-      <c r="M83" s="11"/>
-      <c r="N83" s="11"/>
-      <c r="O83" s="11"/>
-    </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D83" s="11"/>
+      <c r="E83" s="11"/>
+      <c r="F83" s="11"/>
+      <c r="G83" s="11"/>
+      <c r="H83" s="14" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="11">
         <v>73</v>
       </c>
@@ -4089,30 +3244,15 @@
       <c r="C84" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="D84" s="11">
-        <v>6</v>
-      </c>
-      <c r="E84" s="11">
-        <v>3</v>
-      </c>
-      <c r="F84" s="11">
-        <v>3</v>
-      </c>
-      <c r="G84" s="11">
-        <v>5</v>
-      </c>
-      <c r="H84" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I84" s="11"/>
-      <c r="J84" s="11"/>
-      <c r="K84" s="11"/>
-      <c r="L84" s="11"/>
-      <c r="M84" s="11"/>
-      <c r="N84" s="11"/>
-      <c r="O84" s="11"/>
-    </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D84" s="11"/>
+      <c r="E84" s="11"/>
+      <c r="F84" s="11"/>
+      <c r="G84" s="11"/>
+      <c r="H84" s="14" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="11">
         <v>74</v>
       </c>
@@ -4122,30 +3262,15 @@
       <c r="C85" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="D85" s="11">
-        <v>3</v>
-      </c>
-      <c r="E85" s="11">
-        <v>5</v>
-      </c>
-      <c r="F85" s="11">
-        <v>7</v>
-      </c>
-      <c r="G85" s="11">
-        <v>7</v>
-      </c>
-      <c r="H85" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I85" s="11"/>
-      <c r="J85" s="11"/>
-      <c r="K85" s="11"/>
-      <c r="L85" s="11"/>
-      <c r="M85" s="11"/>
-      <c r="N85" s="11"/>
-      <c r="O85" s="11"/>
-    </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D85" s="11"/>
+      <c r="E85" s="11"/>
+      <c r="F85" s="11"/>
+      <c r="G85" s="11"/>
+      <c r="H85" s="14" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="11">
         <v>75</v>
       </c>
@@ -4155,30 +3280,15 @@
       <c r="C86" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="D86" s="11">
-        <v>4</v>
-      </c>
-      <c r="E86" s="11">
-        <v>14</v>
-      </c>
-      <c r="F86" s="11">
-        <v>7</v>
-      </c>
-      <c r="G86" s="11">
-        <v>9</v>
-      </c>
-      <c r="H86" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I86" s="11"/>
-      <c r="J86" s="11"/>
-      <c r="K86" s="11"/>
-      <c r="L86" s="11"/>
-      <c r="M86" s="11"/>
-      <c r="N86" s="11"/>
-      <c r="O86" s="11"/>
-    </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D86" s="11"/>
+      <c r="E86" s="11"/>
+      <c r="F86" s="11"/>
+      <c r="G86" s="11"/>
+      <c r="H86" s="14" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="11">
         <v>76</v>
       </c>
@@ -4188,28 +3298,13 @@
       <c r="C87" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="D87" s="11">
-        <v>6</v>
-      </c>
-      <c r="E87" s="11">
-        <v>16</v>
-      </c>
-      <c r="F87" s="11">
-        <v>15</v>
-      </c>
-      <c r="G87" s="11">
-        <v>7</v>
-      </c>
-      <c r="H87" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="I87" s="11"/>
-      <c r="J87" s="11"/>
-      <c r="K87" s="11"/>
-      <c r="L87" s="11"/>
-      <c r="M87" s="11"/>
-      <c r="N87" s="11"/>
-      <c r="O87" s="11"/>
+      <c r="D87" s="11"/>
+      <c r="E87" s="11"/>
+      <c r="F87" s="11"/>
+      <c r="G87" s="11"/>
+      <c r="H87" s="14" t="s">
+        <v>247</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -4227,11 +3322,7 @@
     <mergeCell ref="F8:L8"/>
     <mergeCell ref="F5:L5"/>
   </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="H12" r:id="rId1" xr:uid="{0D4A0A88-C4C3-4A84-B1FF-4D7548398E11}"/>
-    <hyperlink ref="H13:H87" r:id="rId2" display="parthlearner@gmail.com" xr:uid="{F126D5BB-0AA1-4A0F-87C6-0075DC7DA9BD}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>